--- a/Excel Files/COMP_STATEMENT_ASD.xlsx
+++ b/Excel Files/COMP_STATEMENT_ASD.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13350" yWindow="4800" windowWidth="28770" windowHeight="15450" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9240" yWindow="1395" windowWidth="28455" windowHeight="17745" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="51480" yWindow="3555" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="STATEMENT" sheetId="1" state="visible" r:id="rId1"/>
@@ -79,6 +80,7 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -112,7 +114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -452,6 +454,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="hair">
         <color indexed="64"/>
@@ -512,7 +527,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,12 +552,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -564,6 +573,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -602,10 +623,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -706,9 +736,9 @@
     </from>
     <to>
       <col>6</col>
-      <colOff>848583</colOff>
+      <colOff>854298</colOff>
       <row>3</row>
-      <rowOff>180478</rowOff>
+      <rowOff>174763</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -1008,19 +1038,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A2:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
-    <col width="0.7109375" customWidth="1" style="1" min="1" max="1"/>
-    <col width="19.5703125" customWidth="1" style="1" min="2" max="2"/>
-    <col width="13.7109375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="11.85546875" customWidth="1" style="1" min="4" max="4"/>
-    <col width="8.42578125" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="17.85546875" customWidth="1" style="1" min="6" max="6"/>
-    <col width="14.7109375" customWidth="1" style="1" min="7" max="7"/>
+    <col width="0.6640625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="19.5546875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.6640625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="11.88671875" customWidth="1" style="1" min="4" max="4"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="17.88671875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="14.6640625" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="4.15" customHeight="1"/>
+    <row r="1" ht="4.2" customHeight="1"/>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1058,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="4.15" customHeight="1"/>
+    <row r="3" ht="4.2" customHeight="1"/>
     <row r="4">
       <c r="B4" s="2">
         <f>info!B2 &amp; " " &amp; info!B3</f>
@@ -1047,40 +1077,40 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="4.15" customHeight="1"/>
-    <row r="8" ht="4.15" customHeight="1" thickBot="1"/>
+    <row r="7" ht="4.2" customHeight="1"/>
+    <row r="8" ht="4.2" customHeight="1" thickBot="1"/>
     <row r="9">
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sales Performance</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n"/>
+      <c r="C9" s="35" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Final Payment</t>
         </is>
       </c>
-      <c r="F9" s="32" t="n"/>
-      <c r="G9" s="33" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Level 1 Sales</t>
         </is>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="22">
         <f>_xlfn.XLOOKUP("L1_REV", payout!$G:$G, payout!$F:$F)</f>
         <v/>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>Level 1 Payout</t>
         </is>
       </c>
-      <c r="F10" s="29" t="n"/>
+      <c r="F10" s="31" t="n"/>
       <c r="G10" s="7">
         <f>_xlfn.XLOOKUP("L1_PO", payout!G:G,payout!F:F)</f>
         <v/>
@@ -1088,21 +1118,21 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="6" t="n"/>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>Level 2 Sales</t>
         </is>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="23">
         <f>_xlfn.XLOOKUP("L2_REV", payout!$G:$G, payout!$F:$F)</f>
         <v/>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Level 2 Payout</t>
         </is>
       </c>
-      <c r="F11" s="29" t="n"/>
+      <c r="F11" s="31" t="n"/>
       <c r="G11" s="7">
         <f>_xlfn.XLOOKUP("L2_PO",payout!G:G,payout!F:F)</f>
         <v/>
@@ -1115,30 +1145,30 @@
           <t>Total Sales</t>
         </is>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="24">
         <f>SUM(C9:C11)</f>
         <v/>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="14">
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="12">
         <f>SUM(G9:G11)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" thickTop="1">
       <c r="B13" s="2" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="C13" s="15" t="n"/>
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>Other Adjustments</t>
         </is>
       </c>
-      <c r="F13" s="38" t="n"/>
+      <c r="F13" s="40" t="n"/>
       <c r="G13" s="5">
         <f>IFERROR(_xlfn.XLOOKUP("ADJUSTMENTS", payout!G:G,payout!F:F), 0) + IFERROR(_xlfn.XLOOKUP("SPIFF_PO", payout!G:G,payout!F:F), 0)</f>
         <v/>
@@ -1149,13 +1179,13 @@
         <f>IF(G14&gt;0, 1, 0)</f>
         <v/>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Guarantee Adjustment</t>
         </is>
       </c>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="18">
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="16">
         <f>IFERROR(_xlfn.XLOOKUP("GUARANTEE",payout!G:G,payout!F:F), 0)</f>
         <v/>
       </c>
@@ -1165,659 +1195,879 @@
         <f>IF(G15&gt;0, 1, 0)</f>
         <v/>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Final Payout</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n"/>
+      <c r="F15" s="29" t="n"/>
       <c r="G15" s="8">
         <f>_xlfn.XLOOKUP("PO_AMT", payout!G:G,payout!F:F)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1" thickBot="1" thickTop="1">
-      <c r="E16" s="39" t="inlineStr">
+      <c r="E16" s="41" t="inlineStr">
         <is>
           <t>YTD Payout</t>
         </is>
       </c>
-      <c r="F16" s="40" t="n"/>
-      <c r="G16" s="43">
+      <c r="F16" s="42" t="n"/>
+      <c r="G16" s="21">
         <f>_xlfn.XLOOKUP("YTD_PO", payout!G:G,payout!F:F)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1"/>
     <row r="19">
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Opportunity Detail </t>
         </is>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="29" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="C20" s="42" t="n"/>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Opp Name</t>
         </is>
       </c>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="28">
+      <c r="B21" s="30">
         <f>IF(LEN(detail!K2)&lt;1,"",detail!K2)</f>
         <v/>
       </c>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="30">
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="32">
         <f>IF(LEN(detail!M2)&lt;1,"",detail!M2)</f>
         <v/>
       </c>
-      <c r="E21" s="29" t="n"/>
+      <c r="E21" s="31" t="n"/>
       <c r="F21" s="10">
-        <f>DOLLAR(IF(LEN(detail!V2)&lt;1,"",detail!V2), 0) &amp; IF(detail!W2 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G21" s="30">
+        <f>DOLLAR(IF(LEN(detail!W2)&lt;1,"",detail!W2), 0) &amp; IF(detail!X2 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G21" s="32">
         <f>IF(LEN(detail!U2)&lt;1,"",detail!U2)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="28">
+      <c r="B22" s="30">
         <f>IF(LEN(detail!K3)&lt;1,"",detail!K3)</f>
         <v/>
       </c>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="30">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="32">
         <f>IF(LEN(detail!M3)&lt;1,"",detail!M3)</f>
         <v/>
       </c>
-      <c r="E22" s="29" t="n"/>
+      <c r="E22" s="31" t="n"/>
       <c r="F22" s="10">
-        <f>DOLLAR(IF(LEN(detail!V3)&lt;1,"",detail!V3), 0) &amp; IF(detail!W3 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G22" s="30">
+        <f>DOLLAR(IF(LEN(detail!W3)&lt;1,"",detail!W3), 0) &amp; IF(detail!X3 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
         <f>IF(LEN(detail!U3)&lt;1,"",detail!U3)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="28">
+      <c r="B23" s="30">
         <f>IF(LEN(detail!K4)&lt;1,"",detail!K4)</f>
         <v/>
       </c>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="30">
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="32">
         <f>IF(LEN(detail!M4)&lt;1,"",detail!M4)</f>
         <v/>
       </c>
-      <c r="E23" s="29" t="n"/>
+      <c r="E23" s="31" t="n"/>
       <c r="F23" s="10">
-        <f>DOLLAR(IF(LEN(detail!V4)&lt;1,"",detail!V4), 0) &amp; IF(detail!W4 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G23" s="30">
+        <f>DOLLAR(IF(LEN(detail!W4)&lt;1,"",detail!W4), 0) &amp; IF(detail!X4 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G23" s="32">
         <f>IF(LEN(detail!U4)&lt;1,"",detail!U4)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="28">
+      <c r="B24" s="30">
         <f>IF(LEN(detail!K5)&lt;1,"",detail!K5)</f>
         <v/>
       </c>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="30">
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="32">
         <f>IF(LEN(detail!M5)&lt;1,"",detail!M5)</f>
         <v/>
       </c>
-      <c r="E24" s="29" t="n"/>
+      <c r="E24" s="31" t="n"/>
       <c r="F24" s="10">
-        <f>DOLLAR(IF(LEN(detail!V5)&lt;1,"",detail!V5), 0) &amp; IF(detail!W5 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G24" s="30">
+        <f>DOLLAR(IF(LEN(detail!W5)&lt;1,"",detail!W5), 0) &amp; IF(detail!X5 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G24" s="32">
         <f>IF(LEN(detail!U5)&lt;1,"",detail!U5)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="28">
+      <c r="B25" s="30">
         <f>IF(LEN(detail!K6)&lt;1,"",detail!K6)</f>
         <v/>
       </c>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="30">
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="32">
         <f>IF(LEN(detail!M6)&lt;1,"",detail!M6)</f>
         <v/>
       </c>
-      <c r="E25" s="29" t="n"/>
+      <c r="E25" s="31" t="n"/>
       <c r="F25" s="10">
-        <f>DOLLAR(IF(LEN(detail!V6)&lt;1,"",detail!V6), 0) &amp; IF(detail!W6 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
+        <f>DOLLAR(IF(LEN(detail!W6)&lt;1,"",detail!W6), 0) &amp; IF(detail!X6 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G25" s="32">
         <f>IF(LEN(detail!U6)&lt;1,"",detail!U6)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="28">
+      <c r="B26" s="30">
         <f>IF(LEN(detail!K7)&lt;1,"",detail!K7)</f>
         <v/>
       </c>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="30">
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="32">
         <f>IF(LEN(detail!M7)&lt;1,"",detail!M7)</f>
         <v/>
       </c>
-      <c r="E26" s="29" t="n"/>
+      <c r="E26" s="31" t="n"/>
       <c r="F26" s="10">
-        <f>DOLLAR(IF(LEN(detail!V7)&lt;1,"",detail!V7), 0) &amp; IF(detail!W7 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G26" s="30">
+        <f>DOLLAR(IF(LEN(detail!W7)&lt;1,"",detail!W7), 0) &amp; IF(detail!X7 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G26" s="32">
         <f>IF(LEN(detail!U7)&lt;1,"",detail!U7)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="28">
+      <c r="B27" s="30">
         <f>IF(LEN(detail!K8)&lt;1,"",detail!K8)</f>
         <v/>
       </c>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="30">
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="32">
         <f>IF(LEN(detail!M8)&lt;1,"",detail!M8)</f>
         <v/>
       </c>
-      <c r="E27" s="29" t="n"/>
+      <c r="E27" s="31" t="n"/>
       <c r="F27" s="10">
-        <f>DOLLAR(IF(LEN(detail!V8)&lt;1,"",detail!V8), 0) &amp; IF(detail!W8 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G27" s="30">
+        <f>DOLLAR(IF(LEN(detail!W8)&lt;1,"",detail!W8), 0) &amp; IF(detail!X8 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G27" s="32">
         <f>IF(LEN(detail!U8)&lt;1,"",detail!U8)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="28">
+      <c r="B28" s="30">
         <f>IF(LEN(detail!K9)&lt;1,"",detail!K9)</f>
         <v/>
       </c>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="30">
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="32">
         <f>IF(LEN(detail!M9)&lt;1,"",detail!M9)</f>
         <v/>
       </c>
-      <c r="E28" s="29" t="n"/>
+      <c r="E28" s="31" t="n"/>
       <c r="F28" s="10">
-        <f>DOLLAR(IF(LEN(detail!V9)&lt;1,"",detail!V9), 0) &amp; IF(detail!W9 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G28" s="30">
+        <f>DOLLAR(IF(LEN(detail!W9)&lt;1,"",detail!W9), 0) &amp; IF(detail!X9 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G28" s="32">
         <f>IF(LEN(detail!U9)&lt;1,"",detail!U9)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="28">
+      <c r="B29" s="30">
         <f>IF(LEN(detail!K10)&lt;1,"",detail!K10)</f>
         <v/>
       </c>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="30">
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="32">
         <f>IF(LEN(detail!M10)&lt;1,"",detail!M10)</f>
         <v/>
       </c>
-      <c r="E29" s="29" t="n"/>
+      <c r="E29" s="31" t="n"/>
       <c r="F29" s="10">
-        <f>DOLLAR(IF(LEN(detail!V10)&lt;1,"",detail!V10), 0) &amp; IF(detail!W10 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G29" s="30">
+        <f>DOLLAR(IF(LEN(detail!W10)&lt;1,"",detail!W10), 0) &amp; IF(detail!X10 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G29" s="32">
         <f>IF(LEN(detail!U10)&lt;1,"",detail!U10)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="28">
+      <c r="B30" s="30">
         <f>IF(LEN(detail!K11)&lt;1,"",detail!K11)</f>
         <v/>
       </c>
-      <c r="C30" s="29" t="n"/>
-      <c r="D30" s="30">
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="32">
         <f>IF(LEN(detail!M11)&lt;1,"",detail!M11)</f>
         <v/>
       </c>
-      <c r="E30" s="29" t="n"/>
+      <c r="E30" s="31" t="n"/>
       <c r="F30" s="10">
-        <f>DOLLAR(IF(LEN(detail!V11)&lt;1,"",detail!V11), 0) &amp; IF(detail!W11 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G30" s="30">
+        <f>DOLLAR(IF(LEN(detail!W11)&lt;1,"",detail!W11), 0) &amp; IF(detail!X11 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G30" s="32">
         <f>IF(LEN(detail!U11)&lt;1,"",detail!U11)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="28">
+      <c r="B31" s="30">
         <f>IF(LEN(detail!K12)&lt;1,"",detail!K12)</f>
         <v/>
       </c>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="30">
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="32">
         <f>IF(LEN(detail!M12)&lt;1,"",detail!M12)</f>
         <v/>
       </c>
-      <c r="E31" s="29" t="n"/>
+      <c r="E31" s="31" t="n"/>
       <c r="F31" s="10">
-        <f>DOLLAR(IF(LEN(detail!V12)&lt;1,"",detail!V12), 0) &amp; IF(detail!W12 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G31" s="30">
+        <f>DOLLAR(IF(LEN(detail!W12)&lt;1,"",detail!W12), 0) &amp; IF(detail!X12 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G31" s="32">
         <f>IF(LEN(detail!U12)&lt;1,"",detail!U12)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="28">
+      <c r="B32" s="30">
         <f>IF(LEN(detail!K13)&lt;1,"",detail!K13)</f>
         <v/>
       </c>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="30">
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="32">
         <f>IF(LEN(detail!M13)&lt;1,"",detail!M13)</f>
         <v/>
       </c>
-      <c r="E32" s="29" t="n"/>
+      <c r="E32" s="31" t="n"/>
       <c r="F32" s="10">
-        <f>DOLLAR(IF(LEN(detail!V13)&lt;1,"",detail!V13), 0) &amp; IF(detail!W13 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G32" s="30">
+        <f>DOLLAR(IF(LEN(detail!W13)&lt;1,"",detail!W13), 0) &amp; IF(detail!X13 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G32" s="32">
         <f>IF(LEN(detail!U13)&lt;1,"",detail!U13)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="28">
+      <c r="B33" s="30">
         <f>IF(LEN(detail!K14)&lt;1,"",detail!K14)</f>
         <v/>
       </c>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="30">
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="32">
         <f>IF(LEN(detail!M14)&lt;1,"",detail!M14)</f>
         <v/>
       </c>
-      <c r="E33" s="29" t="n"/>
+      <c r="E33" s="31" t="n"/>
       <c r="F33" s="10">
-        <f>DOLLAR(IF(LEN(detail!V14)&lt;1,"",detail!V14), 0) &amp; IF(detail!W14 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G33" s="30">
+        <f>DOLLAR(IF(LEN(detail!W14)&lt;1,"",detail!W14), 0) &amp; IF(detail!X14 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G33" s="32">
         <f>IF(LEN(detail!U14)&lt;1,"",detail!U14)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="28">
+      <c r="B34" s="30">
         <f>IF(LEN(detail!K15)&lt;1,"",detail!K15)</f>
         <v/>
       </c>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="30">
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="32">
         <f>IF(LEN(detail!M15)&lt;1,"",detail!M15)</f>
         <v/>
       </c>
-      <c r="E34" s="29" t="n"/>
+      <c r="E34" s="31" t="n"/>
       <c r="F34" s="10">
-        <f>DOLLAR(IF(LEN(detail!V15)&lt;1,"",detail!V15), 0) &amp; IF(detail!W15 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G34" s="30">
+        <f>DOLLAR(IF(LEN(detail!W15)&lt;1,"",detail!W15), 0) &amp; IF(detail!X15 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G34" s="32">
         <f>IF(LEN(detail!U15)&lt;1,"",detail!U15)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="28">
+      <c r="B35" s="30">
         <f>IF(LEN(detail!K16)&lt;1,"",detail!K16)</f>
         <v/>
       </c>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="30">
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="32">
         <f>IF(LEN(detail!M16)&lt;1,"",detail!M16)</f>
         <v/>
       </c>
-      <c r="E35" s="29" t="n"/>
+      <c r="E35" s="31" t="n"/>
       <c r="F35" s="10">
-        <f>DOLLAR(IF(LEN(detail!V16)&lt;1,"",detail!V16), 0) &amp; IF(detail!W16 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G35" s="30">
+        <f>DOLLAR(IF(LEN(detail!W16)&lt;1,"",detail!W16), 0) &amp; IF(detail!X16 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G35" s="32">
         <f>IF(LEN(detail!U16)&lt;1,"",detail!U16)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="28">
+      <c r="B36" s="30">
         <f>IF(LEN(detail!K17)&lt;1,"",detail!K17)</f>
         <v/>
       </c>
-      <c r="C36" s="29" t="n"/>
-      <c r="D36" s="30">
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="32">
         <f>IF(LEN(detail!M17)&lt;1,"",detail!M17)</f>
         <v/>
       </c>
-      <c r="E36" s="29" t="n"/>
+      <c r="E36" s="31" t="n"/>
       <c r="F36" s="10">
-        <f>DOLLAR(IF(LEN(detail!V17)&lt;1,"",detail!V17), 0) &amp; IF(detail!W17 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G36" s="30">
+        <f>DOLLAR(IF(LEN(detail!W17)&lt;1,"",detail!W17), 0) &amp; IF(detail!X17 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G36" s="32">
         <f>IF(LEN(detail!U17)&lt;1,"",detail!U17)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="28">
+      <c r="B37" s="30">
         <f>IF(LEN(detail!K18)&lt;1,"",detail!K18)</f>
         <v/>
       </c>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="30">
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="32">
         <f>IF(LEN(detail!M18)&lt;1,"",detail!M18)</f>
         <v/>
       </c>
-      <c r="E37" s="29" t="n"/>
+      <c r="E37" s="31" t="n"/>
       <c r="F37" s="10">
-        <f>DOLLAR(IF(LEN(detail!V18)&lt;1,"",detail!V18), 0) &amp; IF(detail!W18 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G37" s="30">
+        <f>DOLLAR(IF(LEN(detail!W18)&lt;1,"",detail!W18), 0) &amp; IF(detail!X18 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G37" s="32">
         <f>IF(LEN(detail!U18)&lt;1,"",detail!U18)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="28">
+      <c r="B38" s="30">
         <f>IF(LEN(detail!K19)&lt;1,"",detail!K19)</f>
         <v/>
       </c>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="30">
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="32">
         <f>IF(LEN(detail!M19)&lt;1,"",detail!M19)</f>
         <v/>
       </c>
-      <c r="E38" s="29" t="n"/>
+      <c r="E38" s="31" t="n"/>
       <c r="F38" s="10">
-        <f>DOLLAR(IF(LEN(detail!V19)&lt;1,"",detail!V19), 0) &amp; IF(detail!W19 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G38" s="30">
+        <f>DOLLAR(IF(LEN(detail!W19)&lt;1,"",detail!W19), 0) &amp; IF(detail!X19 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G38" s="32">
         <f>IF(LEN(detail!U19)&lt;1,"",detail!U19)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="28">
+      <c r="B39" s="30">
         <f>IF(LEN(detail!K20)&lt;1,"",detail!K20)</f>
         <v/>
       </c>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="30">
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="32">
         <f>IF(LEN(detail!M20)&lt;1,"",detail!M20)</f>
         <v/>
       </c>
-      <c r="E39" s="29" t="n"/>
+      <c r="E39" s="31" t="n"/>
       <c r="F39" s="10">
-        <f>DOLLAR(IF(LEN(detail!V20)&lt;1,"",detail!V20), 0) &amp; IF(detail!W20 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G39" s="30">
+        <f>DOLLAR(IF(LEN(detail!W20)&lt;1,"",detail!W20), 0) &amp; IF(detail!X20 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G39" s="32">
         <f>IF(LEN(detail!U20)&lt;1,"",detail!U20)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="28">
+      <c r="B40" s="30">
         <f>IF(LEN(detail!K21)&lt;1,"",detail!K21)</f>
         <v/>
       </c>
-      <c r="C40" s="29" t="n"/>
-      <c r="D40" s="30">
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="32">
         <f>IF(LEN(detail!M21)&lt;1,"",detail!M21)</f>
         <v/>
       </c>
-      <c r="E40" s="29" t="n"/>
+      <c r="E40" s="31" t="n"/>
       <c r="F40" s="10">
-        <f>DOLLAR(IF(LEN(detail!V21)&lt;1,"",detail!V21), 0) &amp; IF(detail!W21 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G40" s="30">
+        <f>DOLLAR(IF(LEN(detail!W21)&lt;1,"",detail!W21), 0) &amp; IF(detail!X21 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G40" s="32">
         <f>IF(LEN(detail!U21)&lt;1,"",detail!U21)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="28">
+      <c r="B41" s="30">
         <f>IF(LEN(detail!K22)&lt;1,"",detail!K22)</f>
         <v/>
       </c>
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="30">
+      <c r="C41" s="31" t="n"/>
+      <c r="D41" s="32">
         <f>IF(LEN(detail!M22)&lt;1,"",detail!M22)</f>
         <v/>
       </c>
-      <c r="E41" s="29" t="n"/>
+      <c r="E41" s="31" t="n"/>
       <c r="F41" s="10">
-        <f>DOLLAR(IF(LEN(detail!V22)&lt;1,"",detail!V22), 0) &amp; IF(detail!W22 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G41" s="30">
+        <f>DOLLAR(IF(LEN(detail!W22)&lt;1,"",detail!W22), 0) &amp; IF(detail!X22 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G41" s="32">
         <f>IF(LEN(detail!U22)&lt;1,"",detail!U22)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="28">
+      <c r="B42" s="30">
         <f>IF(LEN(detail!K23)&lt;1,"",detail!K23)</f>
         <v/>
       </c>
-      <c r="C42" s="29" t="n"/>
-      <c r="D42" s="30">
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="32">
         <f>IF(LEN(detail!M23)&lt;1,"",detail!M23)</f>
         <v/>
       </c>
-      <c r="E42" s="29" t="n"/>
+      <c r="E42" s="31" t="n"/>
       <c r="F42" s="10">
-        <f>DOLLAR(IF(LEN(detail!V23)&lt;1,"",detail!V23), 0) &amp; IF(detail!W23 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G42" s="30">
+        <f>DOLLAR(IF(LEN(detail!W23)&lt;1,"",detail!W23), 0) &amp; IF(detail!X23 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G42" s="32">
         <f>IF(LEN(detail!U23)&lt;1,"",detail!U23)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="28">
+      <c r="B43" s="30">
         <f>IF(LEN(detail!K24)&lt;1,"",detail!K24)</f>
         <v/>
       </c>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="30">
+      <c r="C43" s="31" t="n"/>
+      <c r="D43" s="32">
         <f>IF(LEN(detail!M24)&lt;1,"",detail!M24)</f>
         <v/>
       </c>
-      <c r="E43" s="29" t="n"/>
+      <c r="E43" s="31" t="n"/>
       <c r="F43" s="10">
-        <f>DOLLAR(IF(LEN(detail!V24)&lt;1,"",detail!V24), 0) &amp; IF(detail!W24 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G43" s="30">
+        <f>DOLLAR(IF(LEN(detail!W24)&lt;1,"",detail!W24), 0) &amp; IF(detail!X24 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G43" s="32">
         <f>IF(LEN(detail!U24)&lt;1,"",detail!U24)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="28">
+      <c r="B44" s="30">
         <f>IF(LEN(detail!K25)&lt;1,"",detail!K25)</f>
         <v/>
       </c>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="30">
+      <c r="C44" s="31" t="n"/>
+      <c r="D44" s="32">
         <f>IF(LEN(detail!M25)&lt;1,"",detail!M25)</f>
         <v/>
       </c>
-      <c r="E44" s="29" t="n"/>
+      <c r="E44" s="31" t="n"/>
       <c r="F44" s="10">
-        <f>DOLLAR(IF(LEN(detail!V25)&lt;1,"",detail!V25), 0) &amp; IF(detail!W25 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G44" s="30">
+        <f>DOLLAR(IF(LEN(detail!W25)&lt;1,"",detail!W25), 0) &amp; IF(detail!X25 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G44" s="32">
         <f>IF(LEN(detail!U25)&lt;1,"",detail!U25)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="28">
+      <c r="B45" s="30">
         <f>IF(LEN(detail!K26)&lt;1,"",detail!K26)</f>
         <v/>
       </c>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="30">
+      <c r="C45" s="31" t="n"/>
+      <c r="D45" s="32">
         <f>IF(LEN(detail!M26)&lt;1,"",detail!M26)</f>
         <v/>
       </c>
-      <c r="E45" s="29" t="n"/>
+      <c r="E45" s="31" t="n"/>
       <c r="F45" s="10">
-        <f>DOLLAR(IF(LEN(detail!V26)&lt;1,"",detail!V26), 0) &amp; IF(detail!W26 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G45" s="30">
+        <f>DOLLAR(IF(LEN(detail!W26)&lt;1,"",detail!W26), 0) &amp; IF(detail!X26 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G45" s="32">
         <f>IF(LEN(detail!U26)&lt;1,"",detail!U26)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="28">
+      <c r="B46" s="30">
         <f>IF(LEN(detail!K27)&lt;1,"",detail!K27)</f>
         <v/>
       </c>
-      <c r="C46" s="29" t="n"/>
-      <c r="D46" s="30">
+      <c r="C46" s="31" t="n"/>
+      <c r="D46" s="32">
         <f>IF(LEN(detail!M27)&lt;1,"",detail!M27)</f>
         <v/>
       </c>
-      <c r="E46" s="29" t="n"/>
+      <c r="E46" s="31" t="n"/>
       <c r="F46" s="10">
-        <f>DOLLAR(IF(LEN(detail!V27)&lt;1,"",detail!V27), 0) &amp; IF(detail!W27 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G46" s="30">
+        <f>DOLLAR(IF(LEN(detail!W27)&lt;1,"",detail!W27), 0) &amp; IF(detail!X27 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G46" s="32">
         <f>IF(LEN(detail!U27)&lt;1,"",detail!U27)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B47" s="30">
+        <f>IF(LEN(detail!K28)&lt;1,"",detail!K28)</f>
+        <v/>
+      </c>
+      <c r="C47" s="31" t="n"/>
+      <c r="D47" s="32">
+        <f>IF(LEN(detail!M28)&lt;1,"",detail!M28)</f>
+        <v/>
+      </c>
+      <c r="E47" s="31" t="n"/>
+      <c r="F47" s="10">
+        <f>DOLLAR(IF(LEN(detail!W28)&lt;1,"",detail!W28), 0) &amp; IF(detail!X28 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G47" s="32">
+        <f>IF(LEN(detail!U28)&lt;1,"",detail!U28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="30">
+        <f>IF(LEN(detail!K29)&lt;1,"",detail!K29)</f>
+        <v/>
+      </c>
+      <c r="C48" s="31" t="n"/>
+      <c r="D48" s="32">
+        <f>IF(LEN(detail!M29)&lt;1,"",detail!M29)</f>
+        <v/>
+      </c>
+      <c r="E48" s="31" t="n"/>
+      <c r="F48" s="10">
+        <f>DOLLAR(IF(LEN(detail!W29)&lt;1,"",detail!W29), 0) &amp; IF(detail!X29 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G48" s="32">
+        <f>IF(LEN(detail!U29)&lt;1,"",detail!U29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="30">
+        <f>IF(LEN(detail!K30)&lt;1,"",detail!K30)</f>
+        <v/>
+      </c>
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="32">
+        <f>IF(LEN(detail!M30)&lt;1,"",detail!M30)</f>
+        <v/>
+      </c>
+      <c r="E49" s="31" t="n"/>
+      <c r="F49" s="10">
+        <f>DOLLAR(IF(LEN(detail!W30)&lt;1,"",detail!W30), 0) &amp; IF(detail!X30 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G49" s="32">
+        <f>IF(LEN(detail!U30)&lt;1,"",detail!U30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="30">
+        <f>IF(LEN(detail!K31)&lt;1,"",detail!K31)</f>
+        <v/>
+      </c>
+      <c r="C50" s="31" t="n"/>
+      <c r="D50" s="32">
+        <f>IF(LEN(detail!M31)&lt;1,"",detail!M31)</f>
+        <v/>
+      </c>
+      <c r="E50" s="31" t="n"/>
+      <c r="F50" s="10">
+        <f>DOLLAR(IF(LEN(detail!W31)&lt;1,"",detail!W31), 0) &amp; IF(detail!X31 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G50" s="32">
+        <f>IF(LEN(detail!U31)&lt;1,"",detail!U31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="30">
+        <f>IF(LEN(detail!K32)&lt;1,"",detail!K32)</f>
+        <v/>
+      </c>
+      <c r="C51" s="31" t="n"/>
+      <c r="D51" s="32">
+        <f>IF(LEN(detail!M32)&lt;1,"",detail!M32)</f>
+        <v/>
+      </c>
+      <c r="E51" s="31" t="n"/>
+      <c r="F51" s="10">
+        <f>DOLLAR(IF(LEN(detail!W32)&lt;1,"",detail!W32), 0) &amp; IF(detail!X32 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G51" s="32">
+        <f>IF(LEN(detail!U32)&lt;1,"",detail!U32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="30">
+        <f>IF(LEN(detail!K33)&lt;1,"",detail!K33)</f>
+        <v/>
+      </c>
+      <c r="C52" s="31" t="n"/>
+      <c r="D52" s="32">
+        <f>IF(LEN(detail!M33)&lt;1,"",detail!M33)</f>
+        <v/>
+      </c>
+      <c r="E52" s="31" t="n"/>
+      <c r="F52" s="10">
+        <f>DOLLAR(IF(LEN(detail!W33)&lt;1,"",detail!W33), 0) &amp; IF(detail!X33 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G52" s="32">
+        <f>IF(LEN(detail!U33)&lt;1,"",detail!U33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="30">
+        <f>IF(LEN(detail!K34)&lt;1,"",detail!K34)</f>
+        <v/>
+      </c>
+      <c r="C53" s="31" t="n"/>
+      <c r="D53" s="32">
+        <f>IF(LEN(detail!M34)&lt;1,"",detail!M34)</f>
+        <v/>
+      </c>
+      <c r="E53" s="31" t="n"/>
+      <c r="F53" s="10">
+        <f>DOLLAR(IF(LEN(detail!W34)&lt;1,"",detail!W34), 0) &amp; IF(detail!X34 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G53" s="32">
+        <f>IF(LEN(detail!U34)&lt;1,"",detail!U34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="30">
+        <f>IF(LEN(detail!K35)&lt;1,"",detail!K35)</f>
+        <v/>
+      </c>
+      <c r="C54" s="31" t="n"/>
+      <c r="D54" s="32">
+        <f>IF(LEN(detail!M35)&lt;1,"",detail!M35)</f>
+        <v/>
+      </c>
+      <c r="E54" s="31" t="n"/>
+      <c r="F54" s="10">
+        <f>DOLLAR(IF(LEN(detail!W35)&lt;1,"",detail!W35), 0) &amp; IF(detail!X35 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G54" s="32">
+        <f>IF(LEN(detail!U35)&lt;1,"",detail!U35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="30">
+        <f>IF(LEN(detail!K36)&lt;1,"",detail!K36)</f>
+        <v/>
+      </c>
+      <c r="C55" s="31" t="n"/>
+      <c r="D55" s="32">
+        <f>IF(LEN(detail!M36)&lt;1,"",detail!M36)</f>
+        <v/>
+      </c>
+      <c r="E55" s="31" t="n"/>
+      <c r="F55" s="10">
+        <f>DOLLAR(IF(LEN(detail!W36)&lt;1,"",detail!W36), 0) &amp; IF(detail!X36 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G55" s="32">
+        <f>IF(LEN(detail!U36)&lt;1,"",detail!U36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="30">
+        <f>IF(LEN(detail!K37)&lt;1,"",detail!K37)</f>
+        <v/>
+      </c>
+      <c r="C56" s="31" t="n"/>
+      <c r="D56" s="32">
+        <f>IF(LEN(detail!M37)&lt;1,"",detail!M37)</f>
+        <v/>
+      </c>
+      <c r="E56" s="31" t="n"/>
+      <c r="F56" s="10">
+        <f>DOLLAR(IF(LEN(detail!W37)&lt;1,"",detail!W37), 0) &amp; IF(detail!X37 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G56" s="32">
+        <f>IF(LEN(detail!U37)&lt;1,"",detail!U37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>* An asterisk denotes that the opp includes a rebate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="82">
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="D46:E46"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D40:E40"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="D45:E45"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B19:G19"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D48:E48"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D42:E42"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E16:F16"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="D35:E35"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D44:E44"/>
   </mergeCells>
-  <conditionalFormatting sqref="B21:B46 D21:D46 F21:G46">
+  <conditionalFormatting sqref="B21:B56 D21:D56 F21:G56">
     <cfRule type="containsErrors" priority="1" dxfId="0">
       <formula>ISERROR(B21)</formula>
     </cfRule>
@@ -1838,42 +2088,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>YYYYMM</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="C1" s="44" t="inlineStr">
+      <c r="C1" s="49" t="inlineStr">
         <is>
           <t>YYYYQQ</t>
         </is>
       </c>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>ROLE</t>
         </is>
       </c>
-      <c r="E1" s="44" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="49" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="G1" s="44" t="inlineStr">
+      <c r="G1" s="49" t="inlineStr">
         <is>
           <t>CATEGORY</t>
         </is>
       </c>
-      <c r="H1" s="44" t="inlineStr">
+      <c r="H1" s="49" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1882,7 +2132,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1892,7 +2142,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1906,18 +2156,18 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>63000</v>
+        <v>172500</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>YTD_PO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1927,7 +2177,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1941,18 +2191,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1316.7</v>
+        <v>289704.55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>L1_PO</t>
+          <t>SALES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1962,7 +2212,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1976,18 +2226,18 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6054.83</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L2_PO</t>
+          <t>L1_PO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1997,7 +2247,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2011,18 +2261,18 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>L1_REV</t>
+          <t>L2_PO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2032,7 +2282,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2046,18 +2296,18 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>289704.55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>L2_REV</t>
+          <t>L1_REV</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2067,7 +2317,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2081,18 +2331,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1316.7</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TTL_PO</t>
+          <t>L2_REV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2102,7 +2352,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2116,18 +2366,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18750</v>
+        <v>6054.83</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GUARANTEE</t>
+          <t>TTL_PO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2137,7 +2387,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2155,14 +2405,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PO_AMT</t>
+          <t>GUARANTEE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2172,7 +2422,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2186,18 +2436,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>18750</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>REVENUE_UNITS</t>
+          <t>PO_AMT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2207,7 +2457,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2225,14 +2475,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IMPLANT_UNITS</t>
+          <t>REVENUE_UNITS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2242,7 +2492,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2256,11 +2506,11 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18750</v>
+        <v>13</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>YTD_PO</t>
+          <t>IMPLANT_UNITS</t>
         </is>
       </c>
     </row>
@@ -2276,10 +2526,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="23.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.109375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="23.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2290,7 +2540,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Croxdale, Sean</t>
+          <t>Sean Croxdale</t>
         </is>
       </c>
     </row>
@@ -2362,14 +2612,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>January</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.95" customHeight="1"/>
-    <row r="23" ht="15.95" customHeight="1"/>
-    <row r="24" ht="3.95" customHeight="1"/>
-    <row r="25" ht="3.95" customHeight="1"/>
+          <t>August</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.9" customHeight="1"/>
+    <row r="23" ht="15.9" customHeight="1"/>
+    <row r="24" ht="3.9" customHeight="1"/>
+    <row r="25" ht="3.9" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2381,181 +2631,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>REGION_NM</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>REGION_ID</t>
         </is>
       </c>
-      <c r="C1" s="44" t="inlineStr">
+      <c r="C1" s="49" t="inlineStr">
         <is>
           <t>SALES_CREDIT_ASD_EMAIL</t>
         </is>
       </c>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>SALES_CREDIT_REP_EMAIL</t>
         </is>
       </c>
-      <c r="E1" s="44" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
         <is>
           <t>CLOSEDATE</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="49" t="inlineStr">
         <is>
           <t>CLOSE_YYYYMM</t>
         </is>
       </c>
-      <c r="G1" s="44" t="inlineStr">
+      <c r="G1" s="49" t="inlineStr">
         <is>
           <t>CLOSE_YYYYQQ</t>
         </is>
       </c>
-      <c r="H1" s="44" t="inlineStr">
+      <c r="H1" s="49" t="inlineStr">
         <is>
           <t>IMPLANTED_DT</t>
         </is>
       </c>
-      <c r="I1" s="44" t="inlineStr">
+      <c r="I1" s="49" t="inlineStr">
         <is>
           <t>IMPLANTED_YYYYMM</t>
         </is>
       </c>
-      <c r="J1" s="44" t="inlineStr">
+      <c r="J1" s="49" t="inlineStr">
         <is>
           <t>IMPLANTED_YYYYQQ</t>
         </is>
       </c>
-      <c r="K1" s="44" t="inlineStr">
+      <c r="K1" s="49" t="inlineStr">
         <is>
           <t>ACCOUNT_INDICATION__C</t>
         </is>
       </c>
-      <c r="L1" s="44" t="inlineStr">
+      <c r="L1" s="49" t="inlineStr">
         <is>
           <t>ACT_ID</t>
         </is>
       </c>
-      <c r="M1" s="44" t="inlineStr">
+      <c r="M1" s="49" t="inlineStr">
         <is>
           <t>OPP_NAME</t>
         </is>
       </c>
-      <c r="N1" s="44" t="inlineStr">
+      <c r="N1" s="49" t="inlineStr">
         <is>
           <t>OPP_ID</t>
         </is>
       </c>
-      <c r="O1" s="44" t="inlineStr">
+      <c r="O1" s="49" t="inlineStr">
         <is>
           <t>PHYSICIAN</t>
         </is>
       </c>
-      <c r="P1" s="44" t="inlineStr">
+      <c r="P1" s="49" t="inlineStr">
         <is>
           <t>PHYSICIAN_ID</t>
         </is>
       </c>
-      <c r="Q1" s="44" t="inlineStr">
+      <c r="Q1" s="49" t="inlineStr">
         <is>
           <t>INDICATION_FOR_USE__C</t>
         </is>
       </c>
-      <c r="R1" s="44" t="inlineStr">
+      <c r="R1" s="49" t="inlineStr">
         <is>
           <t>REASON_FOR_IMPLANT__C</t>
         </is>
       </c>
-      <c r="S1" s="44" t="inlineStr">
+      <c r="S1" s="49" t="inlineStr">
         <is>
           <t>ISIMPL</t>
         </is>
       </c>
-      <c r="T1" s="44" t="inlineStr">
+      <c r="T1" s="49" t="inlineStr">
         <is>
           <t>IMPLANT_UNITS</t>
         </is>
       </c>
-      <c r="U1" s="44" t="inlineStr">
+      <c r="U1" s="49" t="inlineStr">
         <is>
           <t>REVENUE_UNITS</t>
         </is>
       </c>
-      <c r="V1" s="44" t="inlineStr">
+      <c r="V1" s="49" t="inlineStr">
         <is>
           <t>SALES</t>
         </is>
       </c>
-      <c r="W1" s="44" t="inlineStr">
+      <c r="W1" s="49" t="inlineStr">
+        <is>
+          <t>SALES_COMMISSIONABLE</t>
+        </is>
+      </c>
+      <c r="X1" s="49" t="inlineStr">
         <is>
           <t>REBATE?</t>
         </is>
       </c>
-      <c r="X1" s="44" t="inlineStr">
+      <c r="Y1" s="49" t="inlineStr">
         <is>
           <t>ASP</t>
         </is>
       </c>
-      <c r="Y1" s="44" t="inlineStr">
+      <c r="Z1" s="49" t="inlineStr">
         <is>
           <t>THRESHOLD</t>
         </is>
       </c>
-      <c r="Z1" s="44" t="inlineStr">
+      <c r="AA1" s="49" t="inlineStr">
         <is>
           <t>PLAN</t>
         </is>
       </c>
-      <c r="AA1" s="44" t="inlineStr">
+      <c r="AB1" s="49" t="inlineStr">
         <is>
           <t>L1 Rate</t>
         </is>
       </c>
-      <c r="AB1" s="44" t="inlineStr">
+      <c r="AC1" s="49" t="inlineStr">
         <is>
           <t>L2 Rate</t>
         </is>
       </c>
-      <c r="AC1" s="44" t="inlineStr">
-        <is>
-          <t>QTD_SALES</t>
-        </is>
-      </c>
-      <c r="AD1" s="44" t="inlineStr">
+      <c r="AD1" s="49" t="inlineStr">
+        <is>
+          <t>QTD_SALES_COMMISSIONABLE</t>
+        </is>
+      </c>
+      <c r="AE1" s="49" t="inlineStr">
         <is>
           <t>QTD_IMPLANT_UNITS</t>
         </is>
       </c>
-      <c r="AE1" s="44" t="inlineStr">
+      <c r="AF1" s="49" t="inlineStr">
         <is>
           <t>QTD_REVENUE_UNITS</t>
         </is>
       </c>
-      <c r="AF1" s="44" t="inlineStr">
+      <c r="AG1" s="49" t="inlineStr">
         <is>
           <t>L1_REV</t>
         </is>
       </c>
-      <c r="AG1" s="44" t="inlineStr">
+      <c r="AH1" s="49" t="inlineStr">
         <is>
           <t>L2_REV</t>
         </is>
       </c>
-      <c r="AH1" s="44" t="inlineStr">
+      <c r="AI1" s="49" t="inlineStr">
         <is>
           <t>L1_PO</t>
         </is>
       </c>
-      <c r="AI1" s="44" t="inlineStr">
+      <c r="AJ1" s="49" t="inlineStr">
         <is>
           <t>L2_PO</t>
         </is>
@@ -2579,63 +2834,63 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>jgonzalez@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E2" s="46" t="n">
-        <v>45670</v>
+          <t>bkelly@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E2" s="51" t="n">
+        <v>45874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
-        </is>
-      </c>
-      <c r="H2" s="46" t="n">
-        <v>45670</v>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H2" s="51" t="n">
+        <v>45870</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hca Houston Hc Kingwood</t>
+          <t>Hca Houston Healthcare Clear Lake</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0014u00001pyZnXAAU</t>
+          <t>0014u00001s9Ep8AAE</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CVR419 022507</t>
+          <t>CRX255 026583</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>006UY00000FPLAHYA5</t>
+          <t>006UY00000NwqnPYAR</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Harsh Patel</t>
+          <t>Gerard Abreo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>003UY00000JFGZNYA5</t>
+          <t>0034u00002ZgaxXAAR</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2661,42 +2916,45 @@
         <v>28000</v>
       </c>
       <c r="W2" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>28000</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1449356.9349</v>
-      </c>
       <c r="Z2" t="n">
-        <v>1932475.9134</v>
+        <v>1672407.12</v>
       </c>
       <c r="AA2" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.0209</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.0418</v>
       </c>
-      <c r="AC2" t="n">
-        <v>28000</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>304509.8572938689</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>28000</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>585.1999999999999</v>
-      </c>
       <c r="AI2" t="n">
+        <v>599.33125</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2718,63 +2976,63 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jgonzalez@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E3" s="46" t="n">
-        <v>45684</v>
+          <t>ahilovsky@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E3" s="51" t="n">
+        <v>45874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
-        </is>
-      </c>
-      <c r="H3" s="46" t="n">
-        <v>45680</v>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H3" s="51" t="n">
+        <v>45874</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025_01</t>
+          <t>2025_08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025_Q1</t>
+          <t>2025_Q3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Methodist Hospital-Houston Methodist</t>
+          <t>Methodist Hospital</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0017000001Lsj1MAAR</t>
+          <t>0014u00001pyU5wAAE</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>IAH01 022315</t>
+          <t>METHSA01 026088</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>006UY00000F0g1qYAB</t>
+          <t>006UY00000Mtf97YAB</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Barry Trachtenberg</t>
+          <t>Michael Kwan</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0034u00002ZgAq7AAF</t>
+          <t>0034u00002XvqFJAAZ</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -2794,48 +3052,1045 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>333185.9936575053</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>599.33125</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ahilovsky@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E4" s="51" t="n">
+        <v>45881</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H4" s="51" t="n">
+        <v>45838</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025_06</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025_Q2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>University Health System</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0010g00001kNUiMAAW</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>UTSA 024747</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>006UY00000KP26MYAT</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Zalmen Blanck</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0034u00002ZgaoxAAB</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="n">
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
         <v>35000</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W4" t="n">
+        <v>35000</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y4" t="n">
         <v>35000</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1449356.9349</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1932475.9134</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="Z4" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.0209</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC4" t="n">
         <v>0.0418</v>
       </c>
-      <c r="AC3" t="n">
-        <v>63000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AD4" t="n">
+        <v>368185.9936575053</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="n">
         <v>35000</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI4" t="n">
         <v>731.5</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jgonzalez@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="n">
+        <v>45884</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="n">
+        <v>45882</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Memorial Hermann Southwest Hospital</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0014u00001u6xJGAAY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>HOU545 025599</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>006UY00000M00Y1YAJ</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Paul Dao</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>003UY00000f0qYUYAY</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>403185.9936575053</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>731.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>jgonzalez@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E6" s="51" t="n">
+        <v>45888</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H6" s="51" t="n">
+        <v>45887</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Hca Houston Hc Kingwood</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0014u00001pyZnXAAU</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CVR419 026157</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>006UY00000N0tk1YAB</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Harsh Patel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>003UY00000JFGZNYA5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>431862.1300211416</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>599.33125</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sherron@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E7" s="51" t="n">
+        <v>45890</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="n">
+        <v>45889</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Heart Hospital Of Austin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0014u00001wpsvFAAQ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>HHA01 026433</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>006UY00000Ncxt3YAB</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Kunjan Bhatt</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0034u00002ZgAwsAAF</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>28000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>460538.266384778</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>28676.13636363636</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>599.33125</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>jgonzalez@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E8" s="51" t="n">
+        <v>45890</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H8" s="51" t="n">
+        <v>45884</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Memorial Hermann Memorial City Medical Center</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0010g00001mL5fJAAS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>MHMC 025786</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>006UY00000MFnADYA1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Phil Berman</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0034u00002gq2KpAAI</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>495538.266384778</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>731.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cfoglia@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>45897</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H9" s="51" t="n">
+        <v>45895</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Chritus Health Mother Frances Tyler</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>001UY00000F6OlNYAV</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>CHMFT 026938</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>006UY00000OhBbtYAF</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Hector Ceccoli</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0034u00002r0KQnAAM</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>530538.266384778</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>731.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>THE SYNDICATE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RE_03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>scroxdale@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>jgonzalez@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E10" s="51" t="n">
+        <v>45898</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="H10" s="51" t="n">
+        <v>45895</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025_08</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2025_Q3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Methodist Hospital-Houston Methodist</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0017000001Lsj1MAAR</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IAH01 025261</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>006UY00000LJdeHYAT</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Rayan Yousefzai</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0034u00002ZgAq3AAF</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1672407.12</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2229876.1599</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>565538.266384778</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>731.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Excel Files/COMP_STATEMENT_ASD.xlsx
+++ b/Excel Files/COMP_STATEMENT_ASD.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="51480" yWindow="2715" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="51480" yWindow="2715" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="STATEMENT" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <numFmt numFmtId="168" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,11 +79,6 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -111,7 +106,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -432,21 +427,6 @@
       </top>
       <bottom style="hair">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -505,7 +485,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -562,9 +542,6 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1050,23 +1027,23 @@
     <row r="7" ht="4.15" customHeight="1"/>
     <row r="8" ht="4.15" customHeight="1" thickBot="1"/>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Sales Performance</t>
         </is>
       </c>
-      <c r="C9" s="38" t="n"/>
+      <c r="C9" s="37" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Final Payment</t>
         </is>
       </c>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="38" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="37" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>Level 1 Sales</t>
         </is>
@@ -1075,12 +1052,12 @@
         <f>_xlfn.XLOOKUP("L1_REV", payout!$G:$G, payout!$F:$F)</f>
         <v/>
       </c>
-      <c r="E10" s="45" t="inlineStr">
+      <c r="E10" s="44" t="inlineStr">
         <is>
           <t>Level 1 Payout</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n"/>
+      <c r="F10" s="29" t="n"/>
       <c r="G10" s="7">
         <f>_xlfn.XLOOKUP("L1_PO", payout!G:G,payout!F:F)</f>
         <v/>
@@ -1088,7 +1065,7 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="6" t="n"/>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>Level 2 Sales</t>
         </is>
@@ -1097,12 +1074,12 @@
         <f>_xlfn.XLOOKUP("L2_REV", payout!$G:$G, payout!$F:$F)</f>
         <v/>
       </c>
-      <c r="E11" s="45" t="inlineStr">
+      <c r="E11" s="44" t="inlineStr">
         <is>
           <t>Level 2 Payout</t>
         </is>
       </c>
-      <c r="F11" s="30" t="n"/>
+      <c r="F11" s="29" t="n"/>
       <c r="G11" s="7">
         <f>_xlfn.XLOOKUP("L2_PO",payout!G:G,payout!F:F)</f>
         <v/>
@@ -1119,12 +1096,12 @@
         <f>SUM(C9:C11)</f>
         <v/>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="F12" s="33" t="n"/>
+      <c r="F12" s="32" t="n"/>
       <c r="G12" s="12">
         <f>SUM(G9:G11)</f>
         <v/>
@@ -1133,12 +1110,12 @@
     <row r="13" ht="17.25" customHeight="1" thickTop="1">
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="15" t="n"/>
-      <c r="E13" s="39" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Other Adjustments</t>
         </is>
       </c>
-      <c r="F13" s="40" t="n"/>
+      <c r="F13" s="39" t="n"/>
       <c r="G13" s="5">
         <f>IFERROR(_xlfn.XLOOKUP("ADJUSTMENTS", payout!G:G,payout!F:F), 0) + IFERROR(_xlfn.XLOOKUP("SPIFF_PO", payout!G:G,payout!F:F), 0)</f>
         <v/>
@@ -1165,24 +1142,24 @@
         <f>IF(G15&gt;0, 1, 0)</f>
         <v/>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Final Payout</t>
         </is>
       </c>
-      <c r="F15" s="33" t="n"/>
+      <c r="F15" s="32" t="n"/>
       <c r="G15" s="8">
         <f>_xlfn.XLOOKUP("PO_AMT", payout!G:G,payout!F:F)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1" thickBot="1" thickTop="1">
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>YTD Payout</t>
         </is>
       </c>
-      <c r="F16" s="35" t="n"/>
+      <c r="F16" s="34" t="n"/>
       <c r="G16" s="21">
         <f>_xlfn.XLOOKUP("YTD_PO", payout!G:G,payout!F:F)</f>
         <v/>
@@ -1190,30 +1167,30 @@
     </row>
     <row r="17" ht="17.25" customHeight="1"/>
     <row r="19">
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Opportunity Detail </t>
         </is>
       </c>
-      <c r="C19" s="44" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="30" t="n"/>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="29" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="C20" s="42" t="n"/>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Opp Name</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n"/>
+      <c r="E20" s="27" t="n"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -1221,727 +1198,727 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Rev Units</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="29">
-        <f>IF(LEN(detail!K2)&lt;1,"",detail!K2)</f>
-        <v/>
-      </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="31">
+      <c r="B21" s="28">
         <f>IF(LEN(detail!M2)&lt;1,"",detail!M2)</f>
         <v/>
       </c>
-      <c r="E21" s="30" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="30">
+        <f>IF(LEN(detail!P2)&lt;1,"",detail!P2)</f>
+        <v/>
+      </c>
+      <c r="E21" s="29" t="n"/>
       <c r="F21" s="10">
-        <f>DOLLAR(IF(LEN(detail!W2)&lt;1,"",detail!W2), 0) &amp; IF(detail!X2 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G21" s="31">
-        <f>IF(LEN(detail!U2)&lt;1,"",detail!U2)</f>
+        <f>DOLLAR(IF(LEN(detail!Z2)&lt;1,"",detail!Z2), 0) &amp; IF(detail!AA2 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G21" s="30">
+        <f>IF(LEN(detail!X2)&lt;1,"",detail!X2)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="29">
-        <f>IF(LEN(detail!K3)&lt;1,"",detail!K3)</f>
-        <v/>
-      </c>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="31">
+      <c r="B22" s="28">
         <f>IF(LEN(detail!M3)&lt;1,"",detail!M3)</f>
         <v/>
       </c>
-      <c r="E22" s="30" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="30">
+        <f>IF(LEN(detail!P3)&lt;1,"",detail!P3)</f>
+        <v/>
+      </c>
+      <c r="E22" s="29" t="n"/>
       <c r="F22" s="10">
-        <f>DOLLAR(IF(LEN(detail!W3)&lt;1,"",detail!W3), 0) &amp; IF(detail!X3 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G22" s="31">
-        <f>IF(LEN(detail!U3)&lt;1,"",detail!U3)</f>
+        <f>DOLLAR(IF(LEN(detail!Z3)&lt;1,"",detail!Z3), 0) &amp; IF(detail!AA3 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G22" s="30">
+        <f>IF(LEN(detail!X3)&lt;1,"",detail!X3)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="29">
-        <f>IF(LEN(detail!K4)&lt;1,"",detail!K4)</f>
-        <v/>
-      </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="31">
+      <c r="B23" s="28">
         <f>IF(LEN(detail!M4)&lt;1,"",detail!M4)</f>
         <v/>
       </c>
-      <c r="E23" s="30" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="30">
+        <f>IF(LEN(detail!P4)&lt;1,"",detail!P4)</f>
+        <v/>
+      </c>
+      <c r="E23" s="29" t="n"/>
       <c r="F23" s="10">
-        <f>DOLLAR(IF(LEN(detail!W4)&lt;1,"",detail!W4), 0) &amp; IF(detail!X4 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G23" s="31">
-        <f>IF(LEN(detail!U4)&lt;1,"",detail!U4)</f>
+        <f>DOLLAR(IF(LEN(detail!Z4)&lt;1,"",detail!Z4), 0) &amp; IF(detail!AA4 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G23" s="30">
+        <f>IF(LEN(detail!X4)&lt;1,"",detail!X4)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="29">
-        <f>IF(LEN(detail!K5)&lt;1,"",detail!K5)</f>
-        <v/>
-      </c>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="31">
+      <c r="B24" s="28">
         <f>IF(LEN(detail!M5)&lt;1,"",detail!M5)</f>
         <v/>
       </c>
-      <c r="E24" s="30" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="30">
+        <f>IF(LEN(detail!P5)&lt;1,"",detail!P5)</f>
+        <v/>
+      </c>
+      <c r="E24" s="29" t="n"/>
       <c r="F24" s="10">
-        <f>DOLLAR(IF(LEN(detail!W5)&lt;1,"",detail!W5), 0) &amp; IF(detail!X5 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G24" s="31">
-        <f>IF(LEN(detail!U5)&lt;1,"",detail!U5)</f>
+        <f>DOLLAR(IF(LEN(detail!Z5)&lt;1,"",detail!Z5), 0) &amp; IF(detail!AA5 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G24" s="30">
+        <f>IF(LEN(detail!X5)&lt;1,"",detail!X5)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="29">
-        <f>IF(LEN(detail!K6)&lt;1,"",detail!K6)</f>
-        <v/>
-      </c>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="31">
+      <c r="B25" s="28">
         <f>IF(LEN(detail!M6)&lt;1,"",detail!M6)</f>
         <v/>
       </c>
-      <c r="E25" s="30" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="30">
+        <f>IF(LEN(detail!P6)&lt;1,"",detail!P6)</f>
+        <v/>
+      </c>
+      <c r="E25" s="29" t="n"/>
       <c r="F25" s="10">
-        <f>DOLLAR(IF(LEN(detail!W6)&lt;1,"",detail!W6), 0) &amp; IF(detail!X6 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G25" s="31">
-        <f>IF(LEN(detail!U6)&lt;1,"",detail!U6)</f>
+        <f>DOLLAR(IF(LEN(detail!Z6)&lt;1,"",detail!Z6), 0) &amp; IF(detail!AA6 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G25" s="30">
+        <f>IF(LEN(detail!X6)&lt;1,"",detail!X6)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="29">
-        <f>IF(LEN(detail!K7)&lt;1,"",detail!K7)</f>
-        <v/>
-      </c>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="31">
+      <c r="B26" s="28">
         <f>IF(LEN(detail!M7)&lt;1,"",detail!M7)</f>
         <v/>
       </c>
-      <c r="E26" s="30" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="30">
+        <f>IF(LEN(detail!P7)&lt;1,"",detail!P7)</f>
+        <v/>
+      </c>
+      <c r="E26" s="29" t="n"/>
       <c r="F26" s="10">
-        <f>DOLLAR(IF(LEN(detail!W7)&lt;1,"",detail!W7), 0) &amp; IF(detail!X7 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G26" s="31">
-        <f>IF(LEN(detail!U7)&lt;1,"",detail!U7)</f>
+        <f>DOLLAR(IF(LEN(detail!Z7)&lt;1,"",detail!Z7), 0) &amp; IF(detail!AA7 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>IF(LEN(detail!X7)&lt;1,"",detail!X7)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="29">
-        <f>IF(LEN(detail!K8)&lt;1,"",detail!K8)</f>
-        <v/>
-      </c>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="31">
+      <c r="B27" s="28">
         <f>IF(LEN(detail!M8)&lt;1,"",detail!M8)</f>
         <v/>
       </c>
-      <c r="E27" s="30" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30">
+        <f>IF(LEN(detail!P8)&lt;1,"",detail!P8)</f>
+        <v/>
+      </c>
+      <c r="E27" s="29" t="n"/>
       <c r="F27" s="10">
-        <f>DOLLAR(IF(LEN(detail!W8)&lt;1,"",detail!W8), 0) &amp; IF(detail!X8 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G27" s="31">
-        <f>IF(LEN(detail!U8)&lt;1,"",detail!U8)</f>
+        <f>DOLLAR(IF(LEN(detail!Z8)&lt;1,"",detail!Z8), 0) &amp; IF(detail!AA8 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G27" s="30">
+        <f>IF(LEN(detail!X8)&lt;1,"",detail!X8)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="29">
-        <f>IF(LEN(detail!K9)&lt;1,"",detail!K9)</f>
-        <v/>
-      </c>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="31">
+      <c r="B28" s="28">
         <f>IF(LEN(detail!M9)&lt;1,"",detail!M9)</f>
         <v/>
       </c>
-      <c r="E28" s="30" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="30">
+        <f>IF(LEN(detail!P9)&lt;1,"",detail!P9)</f>
+        <v/>
+      </c>
+      <c r="E28" s="29" t="n"/>
       <c r="F28" s="10">
-        <f>DOLLAR(IF(LEN(detail!W9)&lt;1,"",detail!W9), 0) &amp; IF(detail!X9 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G28" s="31">
-        <f>IF(LEN(detail!U9)&lt;1,"",detail!U9)</f>
+        <f>DOLLAR(IF(LEN(detail!Z9)&lt;1,"",detail!Z9), 0) &amp; IF(detail!AA9 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G28" s="30">
+        <f>IF(LEN(detail!X9)&lt;1,"",detail!X9)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="29">
-        <f>IF(LEN(detail!K10)&lt;1,"",detail!K10)</f>
-        <v/>
-      </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="31">
+      <c r="B29" s="28">
         <f>IF(LEN(detail!M10)&lt;1,"",detail!M10)</f>
         <v/>
       </c>
-      <c r="E29" s="30" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="30">
+        <f>IF(LEN(detail!P10)&lt;1,"",detail!P10)</f>
+        <v/>
+      </c>
+      <c r="E29" s="29" t="n"/>
       <c r="F29" s="10">
-        <f>DOLLAR(IF(LEN(detail!W10)&lt;1,"",detail!W10), 0) &amp; IF(detail!X10 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G29" s="31">
-        <f>IF(LEN(detail!U10)&lt;1,"",detail!U10)</f>
+        <f>DOLLAR(IF(LEN(detail!Z10)&lt;1,"",detail!Z10), 0) &amp; IF(detail!AA10 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>IF(LEN(detail!X10)&lt;1,"",detail!X10)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="29">
-        <f>IF(LEN(detail!K11)&lt;1,"",detail!K11)</f>
-        <v/>
-      </c>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="31">
+      <c r="B30" s="28">
         <f>IF(LEN(detail!M11)&lt;1,"",detail!M11)</f>
         <v/>
       </c>
-      <c r="E30" s="30" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="30">
+        <f>IF(LEN(detail!P11)&lt;1,"",detail!P11)</f>
+        <v/>
+      </c>
+      <c r="E30" s="29" t="n"/>
       <c r="F30" s="10">
-        <f>DOLLAR(IF(LEN(detail!W11)&lt;1,"",detail!W11), 0) &amp; IF(detail!X11 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G30" s="31">
-        <f>IF(LEN(detail!U11)&lt;1,"",detail!U11)</f>
+        <f>DOLLAR(IF(LEN(detail!Z11)&lt;1,"",detail!Z11), 0) &amp; IF(detail!AA11 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G30" s="30">
+        <f>IF(LEN(detail!X11)&lt;1,"",detail!X11)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="29">
-        <f>IF(LEN(detail!K12)&lt;1,"",detail!K12)</f>
-        <v/>
-      </c>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="31">
+      <c r="B31" s="28">
         <f>IF(LEN(detail!M12)&lt;1,"",detail!M12)</f>
         <v/>
       </c>
-      <c r="E31" s="30" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30">
+        <f>IF(LEN(detail!P12)&lt;1,"",detail!P12)</f>
+        <v/>
+      </c>
+      <c r="E31" s="29" t="n"/>
       <c r="F31" s="10">
-        <f>DOLLAR(IF(LEN(detail!W12)&lt;1,"",detail!W12), 0) &amp; IF(detail!X12 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G31" s="31">
-        <f>IF(LEN(detail!U12)&lt;1,"",detail!U12)</f>
+        <f>DOLLAR(IF(LEN(detail!Z12)&lt;1,"",detail!Z12), 0) &amp; IF(detail!AA12 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G31" s="30">
+        <f>IF(LEN(detail!X12)&lt;1,"",detail!X12)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="29">
-        <f>IF(LEN(detail!K13)&lt;1,"",detail!K13)</f>
-        <v/>
-      </c>
-      <c r="C32" s="30" t="n"/>
-      <c r="D32" s="31">
+      <c r="B32" s="28">
         <f>IF(LEN(detail!M13)&lt;1,"",detail!M13)</f>
         <v/>
       </c>
-      <c r="E32" s="30" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="30">
+        <f>IF(LEN(detail!P13)&lt;1,"",detail!P13)</f>
+        <v/>
+      </c>
+      <c r="E32" s="29" t="n"/>
       <c r="F32" s="10">
-        <f>DOLLAR(IF(LEN(detail!W13)&lt;1,"",detail!W13), 0) &amp; IF(detail!X13 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G32" s="31">
-        <f>IF(LEN(detail!U13)&lt;1,"",detail!U13)</f>
+        <f>DOLLAR(IF(LEN(detail!Z13)&lt;1,"",detail!Z13), 0) &amp; IF(detail!AA13 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G32" s="30">
+        <f>IF(LEN(detail!X13)&lt;1,"",detail!X13)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="29">
-        <f>IF(LEN(detail!K14)&lt;1,"",detail!K14)</f>
-        <v/>
-      </c>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="31">
+      <c r="B33" s="28">
         <f>IF(LEN(detail!M14)&lt;1,"",detail!M14)</f>
         <v/>
       </c>
-      <c r="E33" s="30" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="30">
+        <f>IF(LEN(detail!P14)&lt;1,"",detail!P14)</f>
+        <v/>
+      </c>
+      <c r="E33" s="29" t="n"/>
       <c r="F33" s="10">
-        <f>DOLLAR(IF(LEN(detail!W14)&lt;1,"",detail!W14), 0) &amp; IF(detail!X14 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G33" s="31">
-        <f>IF(LEN(detail!U14)&lt;1,"",detail!U14)</f>
+        <f>DOLLAR(IF(LEN(detail!Z14)&lt;1,"",detail!Z14), 0) &amp; IF(detail!AA14 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G33" s="30">
+        <f>IF(LEN(detail!X14)&lt;1,"",detail!X14)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="29">
-        <f>IF(LEN(detail!K15)&lt;1,"",detail!K15)</f>
-        <v/>
-      </c>
-      <c r="C34" s="30" t="n"/>
-      <c r="D34" s="31">
+      <c r="B34" s="28">
         <f>IF(LEN(detail!M15)&lt;1,"",detail!M15)</f>
         <v/>
       </c>
-      <c r="E34" s="30" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="30">
+        <f>IF(LEN(detail!P15)&lt;1,"",detail!P15)</f>
+        <v/>
+      </c>
+      <c r="E34" s="29" t="n"/>
       <c r="F34" s="10">
-        <f>DOLLAR(IF(LEN(detail!W15)&lt;1,"",detail!W15), 0) &amp; IF(detail!X15 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G34" s="31">
-        <f>IF(LEN(detail!U15)&lt;1,"",detail!U15)</f>
+        <f>DOLLAR(IF(LEN(detail!Z15)&lt;1,"",detail!Z15), 0) &amp; IF(detail!AA15 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>IF(LEN(detail!X15)&lt;1,"",detail!X15)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="29">
-        <f>IF(LEN(detail!K16)&lt;1,"",detail!K16)</f>
-        <v/>
-      </c>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="31">
+      <c r="B35" s="28">
         <f>IF(LEN(detail!M16)&lt;1,"",detail!M16)</f>
         <v/>
       </c>
-      <c r="E35" s="30" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="30">
+        <f>IF(LEN(detail!P16)&lt;1,"",detail!P16)</f>
+        <v/>
+      </c>
+      <c r="E35" s="29" t="n"/>
       <c r="F35" s="10">
-        <f>DOLLAR(IF(LEN(detail!W16)&lt;1,"",detail!W16), 0) &amp; IF(detail!X16 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G35" s="31">
-        <f>IF(LEN(detail!U16)&lt;1,"",detail!U16)</f>
+        <f>DOLLAR(IF(LEN(detail!Z16)&lt;1,"",detail!Z16), 0) &amp; IF(detail!AA16 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G35" s="30">
+        <f>IF(LEN(detail!X16)&lt;1,"",detail!X16)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="29">
-        <f>IF(LEN(detail!K17)&lt;1,"",detail!K17)</f>
-        <v/>
-      </c>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="31">
+      <c r="B36" s="28">
         <f>IF(LEN(detail!M17)&lt;1,"",detail!M17)</f>
         <v/>
       </c>
-      <c r="E36" s="30" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="30">
+        <f>IF(LEN(detail!P17)&lt;1,"",detail!P17)</f>
+        <v/>
+      </c>
+      <c r="E36" s="29" t="n"/>
       <c r="F36" s="10">
-        <f>DOLLAR(IF(LEN(detail!W17)&lt;1,"",detail!W17), 0) &amp; IF(detail!X17 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G36" s="31">
-        <f>IF(LEN(detail!U17)&lt;1,"",detail!U17)</f>
+        <f>DOLLAR(IF(LEN(detail!Z17)&lt;1,"",detail!Z17), 0) &amp; IF(detail!AA17 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G36" s="30">
+        <f>IF(LEN(detail!X17)&lt;1,"",detail!X17)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="29">
-        <f>IF(LEN(detail!K18)&lt;1,"",detail!K18)</f>
-        <v/>
-      </c>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="31">
+      <c r="B37" s="28">
         <f>IF(LEN(detail!M18)&lt;1,"",detail!M18)</f>
         <v/>
       </c>
-      <c r="E37" s="30" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="30">
+        <f>IF(LEN(detail!P18)&lt;1,"",detail!P18)</f>
+        <v/>
+      </c>
+      <c r="E37" s="29" t="n"/>
       <c r="F37" s="10">
-        <f>DOLLAR(IF(LEN(detail!W18)&lt;1,"",detail!W18), 0) &amp; IF(detail!X18 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G37" s="31">
-        <f>IF(LEN(detail!U18)&lt;1,"",detail!U18)</f>
+        <f>DOLLAR(IF(LEN(detail!Z18)&lt;1,"",detail!Z18), 0) &amp; IF(detail!AA18 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>IF(LEN(detail!X18)&lt;1,"",detail!X18)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="29">
-        <f>IF(LEN(detail!K19)&lt;1,"",detail!K19)</f>
-        <v/>
-      </c>
-      <c r="C38" s="30" t="n"/>
-      <c r="D38" s="31">
+      <c r="B38" s="28">
         <f>IF(LEN(detail!M19)&lt;1,"",detail!M19)</f>
         <v/>
       </c>
-      <c r="E38" s="30" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="30">
+        <f>IF(LEN(detail!P19)&lt;1,"",detail!P19)</f>
+        <v/>
+      </c>
+      <c r="E38" s="29" t="n"/>
       <c r="F38" s="10">
-        <f>DOLLAR(IF(LEN(detail!W19)&lt;1,"",detail!W19), 0) &amp; IF(detail!X19 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G38" s="31">
-        <f>IF(LEN(detail!U19)&lt;1,"",detail!U19)</f>
+        <f>DOLLAR(IF(LEN(detail!Z19)&lt;1,"",detail!Z19), 0) &amp; IF(detail!AA19 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G38" s="30">
+        <f>IF(LEN(detail!X19)&lt;1,"",detail!X19)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="29">
-        <f>IF(LEN(detail!K20)&lt;1,"",detail!K20)</f>
-        <v/>
-      </c>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="31">
+      <c r="B39" s="28">
         <f>IF(LEN(detail!M20)&lt;1,"",detail!M20)</f>
         <v/>
       </c>
-      <c r="E39" s="30" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="30">
+        <f>IF(LEN(detail!P20)&lt;1,"",detail!P20)</f>
+        <v/>
+      </c>
+      <c r="E39" s="29" t="n"/>
       <c r="F39" s="10">
-        <f>DOLLAR(IF(LEN(detail!W20)&lt;1,"",detail!W20), 0) &amp; IF(detail!X20 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G39" s="31">
-        <f>IF(LEN(detail!U20)&lt;1,"",detail!U20)</f>
+        <f>DOLLAR(IF(LEN(detail!Z20)&lt;1,"",detail!Z20), 0) &amp; IF(detail!AA20 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G39" s="30">
+        <f>IF(LEN(detail!X20)&lt;1,"",detail!X20)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="29">
-        <f>IF(LEN(detail!K21)&lt;1,"",detail!K21)</f>
-        <v/>
-      </c>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="31">
+      <c r="B40" s="28">
         <f>IF(LEN(detail!M21)&lt;1,"",detail!M21)</f>
         <v/>
       </c>
-      <c r="E40" s="30" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="30">
+        <f>IF(LEN(detail!P21)&lt;1,"",detail!P21)</f>
+        <v/>
+      </c>
+      <c r="E40" s="29" t="n"/>
       <c r="F40" s="10">
-        <f>DOLLAR(IF(LEN(detail!W21)&lt;1,"",detail!W21), 0) &amp; IF(detail!X21 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G40" s="31">
-        <f>IF(LEN(detail!U21)&lt;1,"",detail!U21)</f>
+        <f>DOLLAR(IF(LEN(detail!Z21)&lt;1,"",detail!Z21), 0) &amp; IF(detail!AA21 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G40" s="30">
+        <f>IF(LEN(detail!X21)&lt;1,"",detail!X21)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="29">
-        <f>IF(LEN(detail!K22)&lt;1,"",detail!K22)</f>
-        <v/>
-      </c>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31">
+      <c r="B41" s="28">
         <f>IF(LEN(detail!M22)&lt;1,"",detail!M22)</f>
         <v/>
       </c>
-      <c r="E41" s="30" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="30">
+        <f>IF(LEN(detail!P22)&lt;1,"",detail!P22)</f>
+        <v/>
+      </c>
+      <c r="E41" s="29" t="n"/>
       <c r="F41" s="10">
-        <f>DOLLAR(IF(LEN(detail!W22)&lt;1,"",detail!W22), 0) &amp; IF(detail!X22 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G41" s="31">
-        <f>IF(LEN(detail!U22)&lt;1,"",detail!U22)</f>
+        <f>DOLLAR(IF(LEN(detail!Z22)&lt;1,"",detail!Z22), 0) &amp; IF(detail!AA22 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G41" s="30">
+        <f>IF(LEN(detail!X22)&lt;1,"",detail!X22)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="29">
-        <f>IF(LEN(detail!K23)&lt;1,"",detail!K23)</f>
-        <v/>
-      </c>
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="31">
+      <c r="B42" s="28">
         <f>IF(LEN(detail!M23)&lt;1,"",detail!M23)</f>
         <v/>
       </c>
-      <c r="E42" s="30" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="30">
+        <f>IF(LEN(detail!P23)&lt;1,"",detail!P23)</f>
+        <v/>
+      </c>
+      <c r="E42" s="29" t="n"/>
       <c r="F42" s="10">
-        <f>DOLLAR(IF(LEN(detail!W23)&lt;1,"",detail!W23), 0) &amp; IF(detail!X23 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G42" s="31">
-        <f>IF(LEN(detail!U23)&lt;1,"",detail!U23)</f>
+        <f>DOLLAR(IF(LEN(detail!Z23)&lt;1,"",detail!Z23), 0) &amp; IF(detail!AA23 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G42" s="30">
+        <f>IF(LEN(detail!X23)&lt;1,"",detail!X23)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="29">
-        <f>IF(LEN(detail!K24)&lt;1,"",detail!K24)</f>
-        <v/>
-      </c>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31">
+      <c r="B43" s="28">
         <f>IF(LEN(detail!M24)&lt;1,"",detail!M24)</f>
         <v/>
       </c>
-      <c r="E43" s="30" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="30">
+        <f>IF(LEN(detail!P24)&lt;1,"",detail!P24)</f>
+        <v/>
+      </c>
+      <c r="E43" s="29" t="n"/>
       <c r="F43" s="10">
-        <f>DOLLAR(IF(LEN(detail!W24)&lt;1,"",detail!W24), 0) &amp; IF(detail!X24 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G43" s="31">
-        <f>IF(LEN(detail!U24)&lt;1,"",detail!U24)</f>
+        <f>DOLLAR(IF(LEN(detail!Z24)&lt;1,"",detail!Z24), 0) &amp; IF(detail!AA24 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G43" s="30">
+        <f>IF(LEN(detail!X24)&lt;1,"",detail!X24)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="29">
-        <f>IF(LEN(detail!K25)&lt;1,"",detail!K25)</f>
-        <v/>
-      </c>
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="31">
+      <c r="B44" s="28">
         <f>IF(LEN(detail!M25)&lt;1,"",detail!M25)</f>
         <v/>
       </c>
-      <c r="E44" s="30" t="n"/>
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="30">
+        <f>IF(LEN(detail!P25)&lt;1,"",detail!P25)</f>
+        <v/>
+      </c>
+      <c r="E44" s="29" t="n"/>
       <c r="F44" s="10">
-        <f>DOLLAR(IF(LEN(detail!W25)&lt;1,"",detail!W25), 0) &amp; IF(detail!X25 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G44" s="31">
-        <f>IF(LEN(detail!U25)&lt;1,"",detail!U25)</f>
+        <f>DOLLAR(IF(LEN(detail!Z25)&lt;1,"",detail!Z25), 0) &amp; IF(detail!AA25 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G44" s="30">
+        <f>IF(LEN(detail!X25)&lt;1,"",detail!X25)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="29">
-        <f>IF(LEN(detail!K26)&lt;1,"",detail!K26)</f>
-        <v/>
-      </c>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31">
+      <c r="B45" s="28">
         <f>IF(LEN(detail!M26)&lt;1,"",detail!M26)</f>
         <v/>
       </c>
-      <c r="E45" s="30" t="n"/>
+      <c r="C45" s="29" t="n"/>
+      <c r="D45" s="30">
+        <f>IF(LEN(detail!P26)&lt;1,"",detail!P26)</f>
+        <v/>
+      </c>
+      <c r="E45" s="29" t="n"/>
       <c r="F45" s="10">
-        <f>DOLLAR(IF(LEN(detail!W26)&lt;1,"",detail!W26), 0) &amp; IF(detail!X26 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G45" s="31">
-        <f>IF(LEN(detail!U26)&lt;1,"",detail!U26)</f>
+        <f>DOLLAR(IF(LEN(detail!Z26)&lt;1,"",detail!Z26), 0) &amp; IF(detail!AA26 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(LEN(detail!X26)&lt;1,"",detail!X26)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="29">
-        <f>IF(LEN(detail!K27)&lt;1,"",detail!K27)</f>
-        <v/>
-      </c>
-      <c r="C46" s="30" t="n"/>
-      <c r="D46" s="31">
+      <c r="B46" s="28">
         <f>IF(LEN(detail!M27)&lt;1,"",detail!M27)</f>
         <v/>
       </c>
-      <c r="E46" s="30" t="n"/>
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="30">
+        <f>IF(LEN(detail!P27)&lt;1,"",detail!P27)</f>
+        <v/>
+      </c>
+      <c r="E46" s="29" t="n"/>
       <c r="F46" s="10">
-        <f>DOLLAR(IF(LEN(detail!W27)&lt;1,"",detail!W27), 0) &amp; IF(detail!X27 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G46" s="31">
-        <f>IF(LEN(detail!U27)&lt;1,"",detail!U27)</f>
+        <f>DOLLAR(IF(LEN(detail!Z27)&lt;1,"",detail!Z27), 0) &amp; IF(detail!AA27 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G46" s="30">
+        <f>IF(LEN(detail!X27)&lt;1,"",detail!X27)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="29">
-        <f>IF(LEN(detail!K28)&lt;1,"",detail!K28)</f>
-        <v/>
-      </c>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31">
+      <c r="B47" s="28">
         <f>IF(LEN(detail!M28)&lt;1,"",detail!M28)</f>
         <v/>
       </c>
-      <c r="E47" s="30" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="30">
+        <f>IF(LEN(detail!P28)&lt;1,"",detail!P28)</f>
+        <v/>
+      </c>
+      <c r="E47" s="29" t="n"/>
       <c r="F47" s="10">
-        <f>DOLLAR(IF(LEN(detail!W28)&lt;1,"",detail!W28), 0) &amp; IF(detail!X28 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G47" s="31">
-        <f>IF(LEN(detail!U28)&lt;1,"",detail!U28)</f>
+        <f>DOLLAR(IF(LEN(detail!Z28)&lt;1,"",detail!Z28), 0) &amp; IF(detail!AA28 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G47" s="30">
+        <f>IF(LEN(detail!X28)&lt;1,"",detail!X28)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="29">
-        <f>IF(LEN(detail!K29)&lt;1,"",detail!K29)</f>
-        <v/>
-      </c>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="31">
+      <c r="B48" s="28">
         <f>IF(LEN(detail!M29)&lt;1,"",detail!M29)</f>
         <v/>
       </c>
-      <c r="E48" s="30" t="n"/>
+      <c r="C48" s="29" t="n"/>
+      <c r="D48" s="30">
+        <f>IF(LEN(detail!P29)&lt;1,"",detail!P29)</f>
+        <v/>
+      </c>
+      <c r="E48" s="29" t="n"/>
       <c r="F48" s="10">
-        <f>DOLLAR(IF(LEN(detail!W29)&lt;1,"",detail!W29), 0) &amp; IF(detail!X29 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G48" s="31">
-        <f>IF(LEN(detail!U29)&lt;1,"",detail!U29)</f>
+        <f>DOLLAR(IF(LEN(detail!Z29)&lt;1,"",detail!Z29), 0) &amp; IF(detail!AA29 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G48" s="30">
+        <f>IF(LEN(detail!X29)&lt;1,"",detail!X29)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="29">
-        <f>IF(LEN(detail!K30)&lt;1,"",detail!K30)</f>
-        <v/>
-      </c>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31">
+      <c r="B49" s="28">
         <f>IF(LEN(detail!M30)&lt;1,"",detail!M30)</f>
         <v/>
       </c>
-      <c r="E49" s="30" t="n"/>
+      <c r="C49" s="29" t="n"/>
+      <c r="D49" s="30">
+        <f>IF(LEN(detail!P30)&lt;1,"",detail!P30)</f>
+        <v/>
+      </c>
+      <c r="E49" s="29" t="n"/>
       <c r="F49" s="10">
-        <f>DOLLAR(IF(LEN(detail!W30)&lt;1,"",detail!W30), 0) &amp; IF(detail!X30 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G49" s="31">
-        <f>IF(LEN(detail!U30)&lt;1,"",detail!U30)</f>
+        <f>DOLLAR(IF(LEN(detail!Z30)&lt;1,"",detail!Z30), 0) &amp; IF(detail!AA30 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G49" s="30">
+        <f>IF(LEN(detail!X30)&lt;1,"",detail!X30)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="29">
-        <f>IF(LEN(detail!K31)&lt;1,"",detail!K31)</f>
-        <v/>
-      </c>
-      <c r="C50" s="30" t="n"/>
-      <c r="D50" s="31">
+      <c r="B50" s="28">
         <f>IF(LEN(detail!M31)&lt;1,"",detail!M31)</f>
         <v/>
       </c>
-      <c r="E50" s="30" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="30">
+        <f>IF(LEN(detail!P31)&lt;1,"",detail!P31)</f>
+        <v/>
+      </c>
+      <c r="E50" s="29" t="n"/>
       <c r="F50" s="10">
-        <f>DOLLAR(IF(LEN(detail!W31)&lt;1,"",detail!W31), 0) &amp; IF(detail!X31 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G50" s="31">
-        <f>IF(LEN(detail!U31)&lt;1,"",detail!U31)</f>
+        <f>DOLLAR(IF(LEN(detail!Z31)&lt;1,"",detail!Z31), 0) &amp; IF(detail!AA31 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G50" s="30">
+        <f>IF(LEN(detail!X31)&lt;1,"",detail!X31)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="29">
-        <f>IF(LEN(detail!K32)&lt;1,"",detail!K32)</f>
-        <v/>
-      </c>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31">
+      <c r="B51" s="28">
         <f>IF(LEN(detail!M32)&lt;1,"",detail!M32)</f>
         <v/>
       </c>
-      <c r="E51" s="30" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="30">
+        <f>IF(LEN(detail!P32)&lt;1,"",detail!P32)</f>
+        <v/>
+      </c>
+      <c r="E51" s="29" t="n"/>
       <c r="F51" s="10">
-        <f>DOLLAR(IF(LEN(detail!W32)&lt;1,"",detail!W32), 0) &amp; IF(detail!X32 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G51" s="31">
-        <f>IF(LEN(detail!U32)&lt;1,"",detail!U32)</f>
+        <f>DOLLAR(IF(LEN(detail!Z32)&lt;1,"",detail!Z32), 0) &amp; IF(detail!AA32 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G51" s="30">
+        <f>IF(LEN(detail!X32)&lt;1,"",detail!X32)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="29">
-        <f>IF(LEN(detail!K33)&lt;1,"",detail!K33)</f>
-        <v/>
-      </c>
-      <c r="C52" s="30" t="n"/>
-      <c r="D52" s="31">
+      <c r="B52" s="28">
         <f>IF(LEN(detail!M33)&lt;1,"",detail!M33)</f>
         <v/>
       </c>
-      <c r="E52" s="30" t="n"/>
+      <c r="C52" s="29" t="n"/>
+      <c r="D52" s="30">
+        <f>IF(LEN(detail!P33)&lt;1,"",detail!P33)</f>
+        <v/>
+      </c>
+      <c r="E52" s="29" t="n"/>
       <c r="F52" s="10">
-        <f>DOLLAR(IF(LEN(detail!W33)&lt;1,"",detail!W33), 0) &amp; IF(detail!X33 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G52" s="31">
-        <f>IF(LEN(detail!U33)&lt;1,"",detail!U33)</f>
+        <f>DOLLAR(IF(LEN(detail!Z33)&lt;1,"",detail!Z33), 0) &amp; IF(detail!AA33 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G52" s="30">
+        <f>IF(LEN(detail!X33)&lt;1,"",detail!X33)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="29">
-        <f>IF(LEN(detail!K34)&lt;1,"",detail!K34)</f>
-        <v/>
-      </c>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31">
+      <c r="B53" s="28">
         <f>IF(LEN(detail!M34)&lt;1,"",detail!M34)</f>
         <v/>
       </c>
-      <c r="E53" s="30" t="n"/>
+      <c r="C53" s="29" t="n"/>
+      <c r="D53" s="30">
+        <f>IF(LEN(detail!P34)&lt;1,"",detail!P34)</f>
+        <v/>
+      </c>
+      <c r="E53" s="29" t="n"/>
       <c r="F53" s="10">
-        <f>DOLLAR(IF(LEN(detail!W34)&lt;1,"",detail!W34), 0) &amp; IF(detail!X34 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G53" s="31">
-        <f>IF(LEN(detail!U34)&lt;1,"",detail!U34)</f>
+        <f>DOLLAR(IF(LEN(detail!Z34)&lt;1,"",detail!Z34), 0) &amp; IF(detail!AA34 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G53" s="30">
+        <f>IF(LEN(detail!X34)&lt;1,"",detail!X34)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="29">
-        <f>IF(LEN(detail!K35)&lt;1,"",detail!K35)</f>
-        <v/>
-      </c>
-      <c r="C54" s="30" t="n"/>
-      <c r="D54" s="31">
+      <c r="B54" s="28">
         <f>IF(LEN(detail!M35)&lt;1,"",detail!M35)</f>
         <v/>
       </c>
-      <c r="E54" s="30" t="n"/>
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="30">
+        <f>IF(LEN(detail!P35)&lt;1,"",detail!P35)</f>
+        <v/>
+      </c>
+      <c r="E54" s="29" t="n"/>
       <c r="F54" s="10">
-        <f>DOLLAR(IF(LEN(detail!W35)&lt;1,"",detail!W35), 0) &amp; IF(detail!X35 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G54" s="31">
-        <f>IF(LEN(detail!U35)&lt;1,"",detail!U35)</f>
+        <f>DOLLAR(IF(LEN(detail!Z35)&lt;1,"",detail!Z35), 0) &amp; IF(detail!AA35 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G54" s="30">
+        <f>IF(LEN(detail!X35)&lt;1,"",detail!X35)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="29">
-        <f>IF(LEN(detail!K36)&lt;1,"",detail!K36)</f>
-        <v/>
-      </c>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31">
+      <c r="B55" s="28">
         <f>IF(LEN(detail!M36)&lt;1,"",detail!M36)</f>
         <v/>
       </c>
-      <c r="E55" s="30" t="n"/>
+      <c r="C55" s="29" t="n"/>
+      <c r="D55" s="30">
+        <f>IF(LEN(detail!P36)&lt;1,"",detail!P36)</f>
+        <v/>
+      </c>
+      <c r="E55" s="29" t="n"/>
       <c r="F55" s="10">
-        <f>DOLLAR(IF(LEN(detail!W36)&lt;1,"",detail!W36), 0) &amp; IF(detail!X36 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G55" s="31">
-        <f>IF(LEN(detail!U36)&lt;1,"",detail!U36)</f>
+        <f>DOLLAR(IF(LEN(detail!Z36)&lt;1,"",detail!Z36), 0) &amp; IF(detail!AA36 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G55" s="30">
+        <f>IF(LEN(detail!X36)&lt;1,"",detail!X36)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="29">
-        <f>IF(LEN(detail!K37)&lt;1,"",detail!K37)</f>
-        <v/>
-      </c>
-      <c r="C56" s="30" t="n"/>
-      <c r="D56" s="31">
+      <c r="B56" s="28">
         <f>IF(LEN(detail!M37)&lt;1,"",detail!M37)</f>
         <v/>
       </c>
-      <c r="E56" s="30" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="30">
+        <f>IF(LEN(detail!P37)&lt;1,"",detail!P37)</f>
+        <v/>
+      </c>
+      <c r="E56" s="29" t="n"/>
       <c r="F56" s="10">
-        <f>DOLLAR(IF(LEN(detail!W37)&lt;1,"",detail!W37), 0) &amp; IF(detail!X37 = 1, "*", "")</f>
-        <v/>
-      </c>
-      <c r="G56" s="31">
-        <f>IF(LEN(detail!U37)&lt;1,"",detail!U37)</f>
+        <f>DOLLAR(IF(LEN(detail!Z37)&lt;1,"",detail!Z37), 0) &amp; IF(detail!AA37 = 1, "*", "")</f>
+        <v/>
+      </c>
+      <c r="G56" s="30">
+        <f>IF(LEN(detail!X37)&lt;1,"",detail!X37)</f>
         <v/>
       </c>
     </row>
@@ -2107,7 +2084,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2126,11 +2103,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>465500</v>
+        <v>10458</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>YTD_PO</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2119,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2161,11 +2138,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11637.5</v>
+        <v>418337.08</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>L1_PO</t>
+          <t>SALES</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2154,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2196,11 +2173,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>10458.43</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L2_PO</t>
+          <t>L1_PO</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2189,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2231,11 +2208,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>465500</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>L1_REV</t>
+          <t>L2_PO</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2224,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2266,11 +2243,11 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>418337.08</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>L2_REV</t>
+          <t>L1_REV</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2259,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2301,11 +2278,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11637.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TTL_PO</t>
+          <t>L2_REV</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2294,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2336,11 +2313,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11637.5</v>
+        <v>10458.43</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PO_AMT</t>
+          <t>TTL_PO</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2329,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2371,11 +2348,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>10458.43</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>REVENUE_UNITS</t>
+          <t>PO_AMT</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2364,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2406,11 +2383,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IMPLANT_UNITS</t>
+          <t>REVENUE_UNITS</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2441,11 +2418,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11638</v>
+        <v>16</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>YTD_PO</t>
+          <t>IMPLANT_UNITS</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2452,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Parker Knight</t>
+          <t>Mike Brown</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Mike</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2602,150 +2579,165 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>CLOSE_YYYY</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>CLOSE_YYYYQQ</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IMPLANTED_DT</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IMPLANTED_YYYYMM</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>IMPLANTED_YYYYQQ</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IMPLANTED_YYYY</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>ACCOUNT_INDICATION__C</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ACT_ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>DHC_IDN_NAME__C</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>OPP_NAME</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>OPP_ID</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PHYSICIAN</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PHYSICIAN_ID</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>INDICATION_FOR_USE__C</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>REASON_FOR_IMPLANT__C</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ISIMPL</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>IMPLANT_UNITS</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>REVENUE_UNITS</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>SALES</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SALES_COMMISSIONABLE</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>REBATE?</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ASP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>THRESHOLD</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>PLAN</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>L1 Rate</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>L2 Rate</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>QTD_SALES_COMMISSIONABLE</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>QTD_IMPLANT_UNITS</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>QTD_REVENUE_UNITS</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>L1_REV</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>L2_REV</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>L1_PO</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>L2_PO</t>
         </is>
@@ -2754,26 +2746,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>kwolf@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E2" s="48" t="n">
-        <v>46033</v>
+          <t>vsawyer@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E2" s="47" t="n">
+        <v>46030</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2782,140 +2774,155 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H2" s="49" t="n">
-        <v>46031</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="48" t="n">
+        <v>46029</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Moses H. Cone Memorial Hospital</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0017000001VykWTAAZ</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cone 026702</t>
+          <t>Providence St Vincent Medical Center</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>006UY00000OEzXGYA1</t>
+          <t>0017000001PgfGiAAJ</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Michael "Andy" Tillery</t>
+          <t>Providence Swedish (FKA Providence)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0034u00002ZgAlfAAF</t>
+          <t>PDX02 028846</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>006UY00000Txns1YAB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Vidang Nguyen</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>003UY000008RCrhYAG</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
-        <v>31500</v>
-      </c>
-      <c r="W2" t="n">
-        <v>31500</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1500339.63</v>
+        <v>35000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2000452.8402</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD2" t="n">
-        <v>31500</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1</v>
       </c>
-      <c r="AG2" t="n">
-        <v>31500</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="n">
-        <v>787.5</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>875</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dharper@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E3" s="48" t="n">
-        <v>46035</v>
+          <t>ctaylor@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E3" s="47" t="n">
+        <v>46031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2924,127 +2931,155 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="48" t="n">
+        <v>46031</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Ecu Health Medical Center</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0014u00001pyU3PAAU</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ECU01 029341</t>
+          <t>Los Robles Hospital &amp; Medical Center</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>006UY00000VB55mYAD</t>
+          <t>0014u00001pyTyOAAU</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CRX794 026205</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>006UY00000N69PyYAJ</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>David Aliabadi</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0034u00002oXzqPAAS</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
       <c r="V3" t="n">
-        <v>94500</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>94500</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1500339.63</v>
+        <v>28668.5393258427</v>
       </c>
       <c r="AA3" t="n">
-        <v>2000452.8402</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD3" t="n">
-        <v>126000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>4</v>
-      </c>
       <c r="AG3" t="n">
-        <v>94500</v>
+        <v>63668.53932584269</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>2362.5</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
+        <v>28668.5393258427</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>716.7134831460675</v>
+      </c>
+      <c r="AM3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kwolf@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E4" s="48" t="n">
-        <v>46035</v>
+          <t>ctaylor@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="n">
+        <v>46034</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3053,127 +3088,155 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="48" t="n">
+        <v>46031</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Unc Rex Hospital</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0010g00001Xatt7AAB</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>REX 029340</t>
+          <t>Los Robles Hospital &amp; Medical Center</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>006UY00000VAoHrYAL</t>
+          <t>0014u00001pyTyOAAU</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CRX794 027778</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>006UY00000QaSWhYAN</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Carney Chan</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0034u00002s2sEeAAI</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
-        <v>35000</v>
-      </c>
       <c r="W4" t="n">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1500339.63</v>
+        <v>28668.5393258427</v>
       </c>
       <c r="AA4" t="n">
-        <v>2000452.8402</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD4" t="n">
-        <v>161000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>5</v>
-      </c>
       <c r="AG4" t="n">
-        <v>35000</v>
+        <v>92337.07865168538</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>875</v>
+        <v>2</v>
       </c>
       <c r="AJ4" t="n">
+        <v>28668.5393258427</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>716.7134831460675</v>
+      </c>
+      <c r="AM4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>clee@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="n">
-        <v>46043</v>
+          <t>ycruea@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="n">
+        <v>46036</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3182,127 +3245,142 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Atrium Health Cabarrus</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0014u00001pyU3OAAU</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AtrmCab001 029488</t>
+          <t>St Joseph Hospital Orange</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>006UY00000VZ8CBYA1</t>
+          <t>0014u00001pyTy3AAE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Providence Swedish (FKA Providence)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CRX773 029408</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>006UY00000VM5GwYAL</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
         <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>35000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>35000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>35000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1500339.63</v>
+        <v>35000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2000452.8402</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD5" t="n">
-        <v>196000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6</v>
-      </c>
       <c r="AG5" t="n">
+        <v>127337.0786516854</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>35000</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
         <v>875</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AM5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>jbuxton@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E6" s="48" t="n">
-        <v>46044</v>
+          <t>ccraigo@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>46045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3311,140 +3389,150 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H6" s="49" t="n">
-        <v>46036</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="48" t="n">
+        <v>46034</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Musc Health Columbia Medical Center Downtown</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0014u00001pyU5FAAU</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MUSCCola01 029298</t>
+          <t>Usc Arcadia Hospital</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>006UY00000V3fRNYAZ</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Patrick Mccann</t>
+          <t>0014u00001pyTyDAAU</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0034u00002W979mAAB</t>
+          <t>CRX783 029069</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>006UY00000UOkGYYA1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Michael Fong</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0034u00002XPHN0AAP</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>35000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>35000</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>35000</v>
       </c>
       <c r="Z6" t="n">
-        <v>1500339.63</v>
+        <v>35000</v>
       </c>
       <c r="AA6" t="n">
-        <v>2000452.8402</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD6" t="n">
-        <v>231000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7</v>
-      </c>
       <c r="AG6" t="n">
+        <v>162337.0786516854</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>35000</v>
       </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
         <v>875</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AM6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jbuxton@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E7" s="48" t="n">
-        <v>46044</v>
+          <t>jmalberg@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>46048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3453,140 +3541,142 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H7" s="49" t="n">
-        <v>46036</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Musc Health Columbia Medical Center Downtown</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0014u00001pyU5FAAU</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MUSCCola01 029299</t>
+          <t>Ucsf Medical Center</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>006UY00000V3gAXYAZ</t>
+          <t>0014u00001pyZlqAAE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Patrick Mccann</t>
+          <t>University of California Health (AKA UC Health-CA)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0034u00002W979mAAB</t>
+          <t>CVR314 028890</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>006UY00000U3JknYAF</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="Y7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1500339.63</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2000452.8402</v>
-      </c>
       <c r="AB7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE7" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD7" t="n">
-        <v>266000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>8</v>
-      </c>
       <c r="AG7" t="n">
-        <v>35000</v>
+        <v>193837.0786516854</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
-        <v>875</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="AM7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>clee@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E8" s="48" t="n">
-        <v>46045</v>
+          <t>jmalberg@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>46048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3595,127 +3685,142 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Atrium Health - Carolinas Medical Center-Pineville</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0014u00001pyU3TAAU</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>AtrmPine01 029592</t>
+          <t>Ucsf Medical Center</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>006UY00000VmnvqYAB</t>
+          <t>0014u00001pyZlqAAE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>University of California Health (AKA UC Health-CA)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CVR314 029551</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>006UY00000VfcIoYAJ</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
-        <v>35000</v>
-      </c>
-      <c r="W8" t="n">
-        <v>35000</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="Z8" t="n">
-        <v>1500339.63</v>
+        <v>31500</v>
       </c>
       <c r="AA8" t="n">
-        <v>2000452.8402</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE8" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD8" t="n">
-        <v>301000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9</v>
-      </c>
       <c r="AG8" t="n">
-        <v>35000</v>
+        <v>225337.0786516854</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
-        <v>875</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="AM8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dharper@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="n">
-        <v>46045</v>
+          <t>asanfilippo@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="n">
+        <v>46050</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3724,126 +3829,141 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>New Hanover Regional Medical Center</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0014u00001s9EsOAAU</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NHRMC001 029523</t>
+          <t>Loma Linda University Medical Center-Murrieta</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>006UY00000Vc3PdYAJ</t>
+          <t>0014u00001pydEQAAY</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Loma Linda University Health</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CVR457 029621</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>006UY00000VpaArYAJ</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>2</v>
       </c>
-      <c r="V9" t="n">
-        <v>70000</v>
-      </c>
-      <c r="W9" t="n">
-        <v>70000</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
       <c r="Y9" t="n">
-        <v>35000</v>
+        <v>66000</v>
       </c>
       <c r="Z9" t="n">
-        <v>1500339.63</v>
+        <v>66000</v>
       </c>
       <c r="AA9" t="n">
-        <v>2000452.8402</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE9" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD9" t="n">
-        <v>371000</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
+        <v>291337.0786516854</v>
+      </c>
+      <c r="AH9" t="n">
         <v>14</v>
       </c>
-      <c r="AF9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>70000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1750</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AM9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MID-ATLANTIC</t>
+          <t>PACIFIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RE_04</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pknight@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jsantoli@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E10" s="48" t="n">
+          <t>vsawyer@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="n">
         <v>46051</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -3853,101 +3973,404 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026_01</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Piedmont Atlanta Hospital</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0010g00001XatwtAAB</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PAH01 029555</t>
+          <t>Legacy Emanuel Mc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>006UY00000VfsnPYAR</t>
+          <t>0014u00001s7myLAAQ</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Legacy Health</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PDX06 029602</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>006UY00000VnRq1YAF</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>Heart Failure - Reduced Ejection Fraction</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>De novo</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
       <c r="V10" t="n">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>31500</v>
+        <v>32000</v>
       </c>
       <c r="Z10" t="n">
-        <v>1500339.63</v>
+        <v>32000</v>
       </c>
       <c r="AA10" t="n">
-        <v>2000452.8402</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>32000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE10" t="n">
         <v>0.025</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AF10" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD10" t="n">
-        <v>465500</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>14</v>
-      </c>
       <c r="AG10" t="n">
-        <v>94500</v>
+        <v>323337.0786516854</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>2362.5</v>
+        <v>9</v>
       </c>
       <c r="AJ10" t="n">
+        <v>32000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>800</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PACIFIC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RE_07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mbrown@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ycruea@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>46052</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026_01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026_Q1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026_01</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026_Q1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>St Joseph Hospital Orange</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0014u00001pyTy3AAE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Providence Swedish (FKA Providence)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CRX773 029676</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>006UY00000VvRzKYAV</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>358337.0786516854</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>875</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PACIFIC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RE_07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mbrown@cvrx.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jmalberg@cvrx.com</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>46053</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026_01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026_Q1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026_02</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026_Q1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Kaweah Delta Medical Center</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0014u00001s9EpwAAE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Kaweah Health (FKA Kaweah Delta Health Care District)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CRX305 029860</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>006UY00000WRIhZYAX</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Heart Failure - Reduced Ejection Fraction</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>De novo</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1184686.1823</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1579581.5763</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>418337.0786516854</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AM12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Excel Files/COMP_STATEMENT_ASD.xlsx
+++ b/Excel Files/COMP_STATEMENT_ASD.xlsx
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10458</v>
+        <v>493500</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YTD_PO</t>
+          <t>SALES</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2138,11 +2138,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418337.08</v>
+        <v>12337.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>L1_PO</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2173,11 +2173,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10458.43</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L1_PO</t>
+          <t>L2_PO</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2208,11 +2208,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>493500</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>L2_PO</t>
+          <t>L1_REV</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2243,11 +2243,11 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>418337.08</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>L1_REV</t>
+          <t>L2_REV</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2278,11 +2278,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>12337.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>L2_REV</t>
+          <t>TTL_PO</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2313,11 +2313,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10458.43</v>
+        <v>12337.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TTL_PO</t>
+          <t>PO_AMT</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2348,11 +2348,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10458.43</v>
+        <v>15</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PO_AMT</t>
+          <t>REVENUE_UNITS</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2383,11 +2383,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>REVENUE_UNITS</t>
+          <t>IMPLANT_UNITS</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>12338</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IMPLANT_UNITS</t>
+          <t>YTD_PO</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Mike Brown</t>
+          <t>Parker Knight</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Parker</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Knight</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,26 +2746,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vsawyer@cvrx.com</t>
+          <t>kwolf@cvrx.com</t>
         </is>
       </c>
       <c r="E2" s="47" t="n">
-        <v>46030</v>
+        <v>46033</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="I2" s="48" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2802,37 +2802,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Providence St Vincent Medical Center</t>
+          <t>Moses H. Cone Memorial Hospital</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0017000001PgfGiAAJ</t>
+          <t>0017000001VykWTAAZ</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Providence Swedish (FKA Providence)</t>
+          <t>Cone Health (FKA Moses Cone Memorial Health)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PDX02 028846</t>
+          <t>Cone 026702</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>006UY00000Txns1YAB</t>
+          <t>006UY00000OEzXGYA1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Vidang Nguyen</t>
+          <t>Michael "Andy" Tillery</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>003UY000008RCrhYAG</t>
+          <t>0034u00002ZgAlfAAF</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>De novo</t>
+          <t>Replacement</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -2855,22 +2855,22 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="Z2" t="n">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="AC2" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD2" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE2" t="n">
         <v>0.025</v>
@@ -2879,22 +2879,22 @@
         <v>0.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AI2" t="n">
         <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>875</v>
+        <v>787.5</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -2903,26 +2903,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ctaylor@cvrx.com</t>
+          <t>dharper@cvrx.com</t>
         </is>
       </c>
       <c r="E3" s="47" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2939,9 +2939,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I3" s="48" t="n">
-        <v>46031</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2959,37 +2956,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Los Robles Hospital &amp; Medical Center</t>
+          <t>Ecu Health Medical Center</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0014u00001pyTyOAAU</t>
+          <t>0014u00001pyU3PAAU</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Vidant Health (FKA University Health Services)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CRX794 026205</t>
+          <t>ECU01 029341</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>006UY00000N69PyYAJ</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>David Aliabadi</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0034u00002oXzqPAAS</t>
+          <t>006UY00000VB55mYAD</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3003,31 +2990,31 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>94500</v>
       </c>
       <c r="Z3" t="n">
-        <v>28668.5393258427</v>
+        <v>94500</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="AC3" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD3" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE3" t="n">
         <v>0.025</v>
@@ -3036,22 +3023,22 @@
         <v>0.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>63668.53932584269</v>
+        <v>126000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28668.5393258427</v>
+        <v>94500</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>716.7134831460675</v>
+        <v>2362.5</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -3060,26 +3047,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ctaylor@cvrx.com</t>
+          <t>kwolf@cvrx.com</t>
         </is>
       </c>
       <c r="E4" s="47" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3096,9 +3083,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="I4" s="48" t="n">
-        <v>46031</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3116,37 +3100,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Los Robles Hospital &amp; Medical Center</t>
+          <t>Unc Rex Hospital</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0014u00001pyTyOAAU</t>
+          <t>0010g00001Xatt7AAB</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>UNC Health (FKA UNC Health Care)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CRX794 027778</t>
+          <t>REX 029340</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>006UY00000QaSWhYAN</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Carney Chan</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0034u00002s2sEeAAI</t>
+          <t>006UY00000VAoHrYAL</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3160,31 +3134,31 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="Z4" t="n">
-        <v>28668.5393258427</v>
+        <v>35000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD4" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE4" t="n">
         <v>0.025</v>
@@ -3193,22 +3167,22 @@
         <v>0.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>92337.07865168538</v>
+        <v>161000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28668.5393258427</v>
+        <v>35000</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>716.7134831460675</v>
+        <v>875</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -3217,26 +3191,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ycruea@cvrx.com</t>
+          <t>clee@cvrx.com</t>
         </is>
       </c>
       <c r="E5" s="47" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3270,27 +3244,27 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>St Joseph Hospital Orange</t>
+          <t>Atrium Health Cabarrus</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0014u00001pyTy3AAE</t>
+          <t>0014u00001pyU3OAAU</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Providence Swedish (FKA Providence)</t>
+          <t>Atrium Health (FKA Carolinas HealthCare System)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CRX773 029408</t>
+          <t>AtrmCab001 029488</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>006UY00000VM5GwYAL</t>
+          <t>006UY00000VZ8CBYA1</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -3325,10 +3299,10 @@
         <v>35000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD5" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE5" t="n">
         <v>0.025</v>
@@ -3337,13 +3311,13 @@
         <v>0.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>127337.0786516854</v>
+        <v>196000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
         <v>35000</v>
@@ -3361,26 +3335,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ccraigo@cvrx.com</t>
+          <t>jbuxton@cvrx.com</t>
         </is>
       </c>
       <c r="E6" s="47" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3398,7 +3372,7 @@
         </is>
       </c>
       <c r="I6" s="48" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3417,32 +3391,37 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Usc Arcadia Hospital</t>
+          <t>Musc Health Columbia Medical Center Downtown</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0014u00001pyTyDAAU</t>
+          <t>0014u00001pyU5FAAU</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Medical University of South Carolina Health System (AKA MUSC Health)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CRX783 029069</t>
+          <t>MUSCCola01 029298</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>006UY00000UOkGYYA1</t>
+          <t>006UY00000V3fRNYAZ</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Michael Fong</t>
+          <t>Patrick Mccann</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0034u00002XPHN0AAP</t>
+          <t>0034u00002W979mAAB</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -3477,10 +3456,10 @@
         <v>35000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE6" t="n">
         <v>0.025</v>
@@ -3489,13 +3468,13 @@
         <v>0.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>162337.0786516854</v>
+        <v>231000</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ6" t="n">
         <v>35000</v>
@@ -3513,26 +3492,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jmalberg@cvrx.com</t>
+          <t>jbuxton@cvrx.com</t>
         </is>
       </c>
       <c r="E7" s="47" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3549,6 +3528,9 @@
           <t>2026_Q1</t>
         </is>
       </c>
+      <c r="I7" s="48" t="n">
+        <v>46036</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3566,27 +3548,37 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Ucsf Medical Center</t>
+          <t>Musc Health Columbia Medical Center Downtown</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0014u00001pyZlqAAE</t>
+          <t>0014u00001pyU5FAAU</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>University of California Health (AKA UC Health-CA)</t>
+          <t>Medical University of South Carolina Health System (AKA MUSC Health)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CVR314 028890</t>
+          <t>MUSCCola01 029299</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>006UY00000U3JknYAF</t>
+          <t>006UY00000V3gAXYAZ</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Patrick Mccann</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0034u00002W979mAAB</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3600,31 +3592,31 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="Z7" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE7" t="n">
         <v>0.025</v>
@@ -3633,22 +3625,22 @@
         <v>0.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>193837.0786516854</v>
+        <v>266000</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>787.5</v>
+        <v>875</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3657,26 +3649,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>jmalberg@cvrx.com</t>
+          <t>clee@cvrx.com</t>
         </is>
       </c>
       <c r="E8" s="47" t="n">
-        <v>46048</v>
+        <v>46045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3710,27 +3702,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Ucsf Medical Center</t>
+          <t>Atrium Health - Carolinas Medical Center-Pineville</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0014u00001pyZlqAAE</t>
+          <t>0014u00001pyU3TAAU</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>University of California Health (AKA UC Health-CA)</t>
+          <t>Atrium Health (FKA Carolinas HealthCare System)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CVR314 029551</t>
+          <t>AtrmPine01 029592</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>006UY00000VfcIoYAJ</t>
+          <t>006UY00000VmnvqYAB</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3753,22 +3745,22 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="Z8" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE8" t="n">
         <v>0.025</v>
@@ -3777,22 +3769,22 @@
         <v>0.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>225337.0786516854</v>
+        <v>301000</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>31500</v>
+        <v>35000</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>787.5</v>
+        <v>875</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -3801,26 +3793,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>asanfilippo@cvrx.com</t>
+          <t>dharper@cvrx.com</t>
         </is>
       </c>
       <c r="E9" s="47" t="n">
-        <v>46050</v>
+        <v>46045</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3854,27 +3846,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Loma Linda University Medical Center-Murrieta</t>
+          <t>New Hanover Regional Medical Center</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0014u00001pydEQAAY</t>
+          <t>0014u00001s9EsOAAU</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Loma Linda University Health</t>
+          <t>Novant Health</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CVR457 029621</t>
+          <t>NHRMC001 029523</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>006UY00000VpaArYAJ</t>
+          <t>006UY00000Vc3PdYAJ</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3897,22 +3889,22 @@
         <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>66000</v>
+        <v>70000</v>
       </c>
       <c r="Z9" t="n">
-        <v>66000</v>
+        <v>70000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE9" t="n">
         <v>0.025</v>
@@ -3921,22 +3913,22 @@
         <v>0.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>291337.0786516854</v>
+        <v>371000</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>66000</v>
+        <v>70000</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -3945,22 +3937,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>vsawyer@cvrx.com</t>
+          <t>jsantoli@cvrx.com</t>
         </is>
       </c>
       <c r="E10" s="47" t="n">
@@ -3998,27 +3990,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Legacy Emanuel Mc</t>
+          <t>Piedmont Atlanta Hospital</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0014u00001s7myLAAQ</t>
+          <t>0010g00001XatwtAAB</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Legacy Health</t>
+          <t>Piedmont Healthcare System</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PDX06 029602</t>
+          <t>PAH01 029555</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>006UY00000VnRq1YAF</t>
+          <t>006UY00000VfsnPYAR</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4038,25 +4030,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>32000</v>
+        <v>94500</v>
       </c>
       <c r="Z10" t="n">
-        <v>32000</v>
+        <v>94500</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>32000</v>
+        <v>31500</v>
       </c>
       <c r="AC10" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE10" t="n">
         <v>0.025</v>
@@ -4065,22 +4057,22 @@
         <v>0.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>323337.0786516854</v>
+        <v>465500</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32000</v>
+        <v>94500</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>800</v>
+        <v>2362.5</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -4089,26 +4081,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PACIFIC</t>
+          <t>MID-ATLANTIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>pknight@cvrx.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ycruea@cvrx.com</t>
+          <t>beverett@cvrx.com</t>
         </is>
       </c>
       <c r="E11" s="47" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4127,7 +4119,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026_01</t>
+          <t>2026_02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4142,27 +4134,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>St Joseph Hospital Orange</t>
+          <t>Northside Hospital Forsyth</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0014u00001pyTy3AAE</t>
+          <t>0014u00001s9EsgAAE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Providence Swedish (FKA Providence)</t>
+          <t>Northside Hospital System</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CRX773 029676</t>
+          <t>NthsideFor 029567</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>006UY00000VvRzKYAV</t>
+          <t>006UY00000Vhtx3YAB</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4185,22 +4177,22 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="Z11" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1184686.1823</v>
+        <v>1500339.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1579581.5763</v>
+        <v>2000452.8402</v>
       </c>
       <c r="AE11" t="n">
         <v>0.025</v>
@@ -4209,168 +4201,24 @@
         <v>0.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>358337.0786516854</v>
+        <v>493500</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>875</v>
+        <v>700</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PACIFIC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>mbrown@cvrx.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jmalberg@cvrx.com</t>
-        </is>
-      </c>
-      <c r="E12" s="47" t="n">
-        <v>46053</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026_02</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Kaweah Delta Medical Center</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0014u00001s9EpwAAE</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Kaweah Health (FKA Kaweah Delta Health Care District)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>CRX305 029860</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>006UY00000WRIhZYAX</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Heart Failure - Reduced Ejection Fraction</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1184686.1823</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1579581.5763</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>418337.0786516854</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="AM12" t="n">
         <v>0</v>
       </c>
     </row>
